--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB16"/>
+  <dimension ref="A1:CB20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H2" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="I2" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L2" t="n">
         <v>1.29</v>
@@ -881,34 +881,34 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>1.21</v>
       </c>
       <c r="P2" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S2" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V2" t="n">
         <v>2.14</v>
       </c>
       <c r="W2" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="X2" t="n">
         <v>23</v>
@@ -920,7 +920,7 @@
         <v>970</v>
       </c>
       <c r="AA2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB2" t="n">
         <v>24</v>
@@ -947,7 +947,7 @@
         <v>38</v>
       </c>
       <c r="AJ2" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AK2" t="n">
         <v>75</v>
@@ -968,7 +968,7 @@
         <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR2" t="n">
         <v>8.800000000000001</v>
@@ -1016,13 +1016,13 @@
         <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BH2" t="n">
         <v>4.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2" t="n">
         <v>11.5</v>
@@ -1037,7 +1037,7 @@
         <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BO2" t="n">
         <v>1.01</v>
@@ -1061,7 +1061,7 @@
         <v>3.55</v>
       </c>
       <c r="BV2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BW2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-13 09:08:18</t>
+          <t>2026-05-13 12:13:51</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>2.42</v>
       </c>
       <c r="H3" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="I3" t="n">
         <v>3.1</v>
@@ -1129,7 +1129,7 @@
         <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="M3" t="n">
         <v>1.04</v>
@@ -1165,10 +1165,10 @@
         <v>1.7</v>
       </c>
       <c r="X3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z3" t="n">
         <v>24</v>
@@ -1246,10 +1246,10 @@
         <v>16</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA3" t="n">
         <v>30</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-13 09:08:18</t>
+          <t>2026-05-13 12:13:51</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
@@ -1383,212 +1383,212 @@
         <v>4.6</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P4" t="n">
         <v>2.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-13 09:08:18</t>
+          <t>2026-05-13 12:13:51</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-13 09:08:18</t>
+          <t>2026-05-13 12:13:51</t>
         </is>
       </c>
     </row>
@@ -1876,13 +1876,13 @@
         <v>1.66</v>
       </c>
       <c r="G6" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J6" t="n">
         <v>3.95</v>
@@ -1891,212 +1891,212 @@
         <v>4.4</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-13 09:08:18</t>
+          <t>2026-05-13 12:13:51</t>
         </is>
       </c>
     </row>
@@ -2139,218 +2139,218 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="K7" t="n">
         <v>6.2</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P7" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-13 09:08:18</t>
+          <t>2026-05-13 12:13:51</t>
         </is>
       </c>
     </row>
@@ -2384,227 +2384,227 @@
         <v>1.68</v>
       </c>
       <c r="G8" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="H8" t="n">
         <v>5.1</v>
       </c>
       <c r="I8" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J8" t="n">
         <v>3.8</v>
       </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P8" t="n">
         <v>1.96</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-13 09:08:18</t>
+          <t>2026-05-13 12:13:51</t>
         </is>
       </c>
     </row>
@@ -2653,212 +2653,212 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P9" t="n">
         <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-13 09:08:18</t>
+          <t>2026-05-13 12:13:51</t>
         </is>
       </c>
     </row>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="G10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
         <v>1.93</v>
@@ -2907,16 +2907,16 @@
         <v>4.7</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P10" t="n">
         <v>1.97</v>
@@ -2925,194 +2925,194 @@
         <v>1.8</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="BM10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BP10" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BS10" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BX10" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BY10" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-13 09:08:18</t>
+          <t>2026-05-13 12:13:51</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>870</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-13 09:08:18</t>
+          <t>2026-05-13 12:13:51</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,36 +3383,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13:15:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Kolding IF</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al-Feiha</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.71</v>
+        <v>3.8</v>
       </c>
       <c r="G12" t="n">
-        <v>1.85</v>
+        <v>4.9</v>
       </c>
       <c r="H12" t="n">
-        <v>5.1</v>
+        <v>1.86</v>
       </c>
       <c r="I12" t="n">
-        <v>6.4</v>
+        <v>2.04</v>
       </c>
       <c r="J12" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.77</v>
+        <v>2.32</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.1</v>
+        <v>1.52</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-13 09:08:18</t>
+          <t>2026-05-13 12:13:51</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,36 +3637,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B93 Copenhagen</t>
+          <t>Zaglebie Lubin</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AaB</t>
+          <t>Pogon Szczecin</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="G13" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="H13" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="I13" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="J13" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="K13" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-13 09:08:18</t>
+          <t>2026-05-13 12:13:51</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,36 +3891,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>13:15:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Widzew Lodz</t>
+          <t>Al-Feiha</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.46</v>
+        <v>1.71</v>
       </c>
       <c r="G14" t="n">
-        <v>2.96</v>
+        <v>1.85</v>
       </c>
       <c r="H14" t="n">
-        <v>2.92</v>
+        <v>5.1</v>
       </c>
       <c r="I14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J14" t="n">
         <v>3.65</v>
       </c>
-      <c r="J14" t="n">
-        <v>3.15</v>
-      </c>
       <c r="K14" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-13 09:08:18</t>
+          <t>2026-05-13 12:13:51</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,36 +4145,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>B93 Copenhagen</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nacional (Par)</t>
+          <t>AaB</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,261 +4382,1277 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-13 09:08:18</t>
+          <t>2026-05-13 12:13:51</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Al-Taawoun Buraidah</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Al Riyadh SC</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:13:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Polish Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Korona Kielce</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Widzew Lodz</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:13:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>English Premier League</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>36</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>85</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>28</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:13:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>17:00:00</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Rubio Nu</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Nacional (Par)</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:13:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Sportivo Trinidense</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Cerro Porteno</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB16" t="inlineStr">
-        <is>
-          <t>2026-05-13 09:08:18</t>
+      <c r="Q20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:13:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB63"/>
+  <dimension ref="A1:CB65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,46 +857,46 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G2" t="n">
         <v>6.4</v>
       </c>
       <c r="H2" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="I2" t="n">
         <v>1.85</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="Q2" t="n">
         <v>1.69</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="T2" t="n">
         <v>1.61</v>
@@ -980,7 +980,7 @@
         <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV2" t="n">
         <v>7.6</v>
@@ -1016,7 +1016,7 @@
         <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH2" t="n">
         <v>4.6</v>
@@ -1043,7 +1043,7 @@
         <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BQ2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>2.42</v>
       </c>
       <c r="H3" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="I3" t="n">
         <v>3.1</v>
@@ -1126,7 +1126,7 @@
         <v>3.9</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>1.31</v>
@@ -1135,16 +1135,16 @@
         <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O3" t="n">
         <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R3" t="n">
         <v>1.55</v>
@@ -1153,10 +1153,10 @@
         <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U3" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V3" t="n">
         <v>1.47</v>
@@ -1180,7 +1180,7 @@
         <v>14.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
         <v>13.5</v>
@@ -1204,7 +1204,7 @@
         <v>34</v>
       </c>
       <c r="AK3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL3" t="n">
         <v>30</v>
@@ -1231,7 +1231,7 @@
         <v>10.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU3" t="n">
         <v>8.199999999999999</v>
@@ -1246,10 +1246,10 @@
         <v>16</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA3" t="n">
         <v>30</v>
@@ -1264,7 +1264,7 @@
         <v>26</v>
       </c>
       <c r="BE3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF3" t="n">
         <v>12</v>
@@ -1294,7 +1294,7 @@
         <v>5.7</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP3" t="n">
         <v>16.5</v>
@@ -1312,7 +1312,7 @@
         <v>6.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV3" t="n">
         <v>21</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -1395,13 +1395,13 @@
         <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q4" t="n">
         <v>1.53</v>
       </c>
       <c r="R4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S4" t="n">
         <v>2.3</v>
@@ -1452,7 +1452,7 @@
         <v>15.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ4" t="n">
         <v>28</v>
@@ -1473,13 +1473,13 @@
         <v>28</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ4" t="n">
         <v>18</v>
       </c>
       <c r="AR4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS4" t="n">
         <v>6.8</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -1619,58 +1619,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="I5" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P5" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U5" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="W5" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X5" t="n">
         <v>21</v>
@@ -1685,10 +1685,10 @@
         <v>20</v>
       </c>
       <c r="AB5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD5" t="n">
         <v>12</v>
@@ -1700,7 +1700,7 @@
         <v>60</v>
       </c>
       <c r="AG5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH5" t="n">
         <v>25</v>
@@ -1709,19 +1709,19 @@
         <v>42</v>
       </c>
       <c r="AJ5" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AK5" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AL5" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AM5" t="n">
         <v>130</v>
       </c>
       <c r="AN5" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AO5" t="n">
         <v>11</v>
@@ -1736,55 +1736,55 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AS5" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AU5" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV5" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AW5" t="n">
         <v>14.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AZ5" t="n">
         <v>17.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH5" t="n">
         <v>4.3</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="BJ5" t="n">
         <v>12.5</v>
@@ -1799,7 +1799,7 @@
         <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BO5" t="n">
         <v>1.01</v>
@@ -1817,32 +1817,32 @@
         <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BV5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BW5" t="n">
         <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BY5" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CA5" t="n">
         <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>1.66</v>
       </c>
       <c r="G6" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H6" t="n">
         <v>5.3</v>
@@ -1906,7 +1906,7 @@
         <v>2.02</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="R6" t="n">
         <v>1.4</v>
@@ -1924,7 +1924,7 @@
         <v>1.18</v>
       </c>
       <c r="W6" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X6" t="n">
         <v>20</v>
@@ -1948,7 +1948,7 @@
         <v>26</v>
       </c>
       <c r="AE6" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF6" t="n">
         <v>12.5</v>
@@ -1987,10 +1987,10 @@
         <v>16.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT6" t="n">
         <v>7.6</v>
@@ -2053,7 +2053,7 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO6" t="n">
         <v>3.35</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>1.4</v>
       </c>
       <c r="G7" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="H7" t="n">
         <v>6.8</v>
@@ -2157,22 +2157,22 @@
         <v>1.15</v>
       </c>
       <c r="P7" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="R7" t="n">
         <v>1.72</v>
       </c>
       <c r="S7" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="T7" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="U7" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
         <v>1.13</v>
@@ -2190,7 +2190,7 @@
         <v>75</v>
       </c>
       <c r="AA7" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AB7" t="n">
         <v>15.5</v>
@@ -2232,7 +2232,7 @@
         <v>4.9</v>
       </c>
       <c r="AO7" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP7" t="n">
         <v>4.5</v>
@@ -2244,7 +2244,7 @@
         <v>4.7</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT7" t="n">
         <v>10.5</v>
@@ -2283,7 +2283,7 @@
         <v>4.8</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BG7" t="n">
         <v>4.8</v>
@@ -2313,10 +2313,10 @@
         <v>3.4</v>
       </c>
       <c r="BP7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
         <v>23</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -2423,10 +2423,10 @@
         <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="U8" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="V8" t="n">
         <v>1.2</v>
@@ -2435,7 +2435,7 @@
         <v>2.22</v>
       </c>
       <c r="X8" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="Y8" t="n">
         <v>23</v>
@@ -2468,7 +2468,7 @@
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="n">
         <v>23</v>
@@ -2477,7 +2477,7 @@
         <v>23</v>
       </c>
       <c r="AL8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM8" t="n">
         <v>130</v>
@@ -2489,28 +2489,28 @@
         <v>100</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>15.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV8" t="n">
         <v>17.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AX8" t="n">
         <v>9</v>
@@ -2522,16 +2522,16 @@
         <v>17</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BB8" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC8" t="n">
         <v>15.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BE8" t="n">
         <v>4.1</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -2919,7 +2919,7 @@
         <v>1.28</v>
       </c>
       <c r="P10" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
         <v>1.28</v>
@@ -2931,10 +2931,10 @@
         <v>1.28</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G11" t="n">
         <v>4.3</v>
@@ -3239,7 +3239,7 @@
         <v>55</v>
       </c>
       <c r="AL11" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
         <v>1.2</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Q13" t="n">
         <v>1.2</v>
@@ -3690,7 +3690,7 @@
         <v>1.08</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="T13" t="n">
         <v>1.11</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -4183,13 +4183,13 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O15" t="n">
         <v>1.25</v>
       </c>
       <c r="P15" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q15" t="n">
         <v>1.25</v>
@@ -4198,7 +4198,7 @@
         <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>1.25</v>
+        <v>3.5</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
         <v>3.65</v>
       </c>
       <c r="K17" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="L17" t="n">
         <v>1.31</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -5438,10 +5438,10 @@
         <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J20" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K20" t="n">
         <v>4.5</v>
@@ -5462,13 +5462,13 @@
         <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="R20" t="n">
         <v>1.58</v>
       </c>
       <c r="S20" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T20" t="n">
         <v>1.49</v>
@@ -5480,7 +5480,7 @@
         <v>1.8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="X20" t="n">
         <v>28</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
         <v>2.6</v>
       </c>
       <c r="I21" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="J21" t="n">
         <v>3.5</v>
@@ -5704,7 +5704,7 @@
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N21" t="n">
         <v>3.9</v>
@@ -5722,7 +5722,7 @@
         <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
         <v>2.54</v>
       </c>
       <c r="G24" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="H24" t="n">
         <v>2.54</v>
@@ -6484,7 +6484,7 @@
         <v>1.57</v>
       </c>
       <c r="S24" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="T24" t="n">
         <v>1.01</v>
@@ -6496,7 +6496,7 @@
         <v>1.54</v>
       </c>
       <c r="W24" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -6702,43 +6702,43 @@
         <v>5.8</v>
       </c>
       <c r="G25" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="H25" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="I25" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="J25" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="K25" t="n">
-        <v>950</v>
+        <v>6</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>3.75</v>
+        <v>1.92</v>
       </c>
       <c r="O25" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="P25" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="T25" t="n">
         <v>1.82</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G26" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H26" t="n">
         <v>2</v>
@@ -6968,7 +6968,7 @@
         <v>4.2</v>
       </c>
       <c r="K26" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -6983,7 +6983,7 @@
         <v>1.14</v>
       </c>
       <c r="P26" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q26" t="n">
         <v>1.42</v>
@@ -6992,7 +6992,7 @@
         <v>1.81</v>
       </c>
       <c r="S26" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T26" t="n">
         <v>1.38</v>
@@ -7004,7 +7004,7 @@
         <v>1.85</v>
       </c>
       <c r="W26" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X26" t="n">
         <v>34</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -7452,226 +7452,226 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Versailles 78 FC</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Villefranche Beaujolais</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.39</v>
+        <v>1.81</v>
       </c>
       <c r="G28" t="n">
-        <v>1.58</v>
+        <v>2.08</v>
       </c>
       <c r="H28" t="n">
-        <v>6.8</v>
+        <v>4</v>
       </c>
       <c r="I28" t="n">
-        <v>10</v>
+        <v>5.6</v>
       </c>
       <c r="J28" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K28" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="L28" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="M28" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N28" t="n">
-        <v>1.1</v>
+        <v>3.35</v>
       </c>
       <c r="O28" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="P28" t="n">
-        <v>2.22</v>
+        <v>1.94</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="R28" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>1.05</v>
+        <v>2.8</v>
       </c>
       <c r="T28" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="U28" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="V28" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="W28" t="n">
-        <v>2.72</v>
+        <v>1.94</v>
       </c>
       <c r="X28" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="Z28" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AA28" t="n">
-        <v>290</v>
+        <v>120</v>
       </c>
       <c r="AB28" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="AE28" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL28" t="n">
         <v>140</v>
       </c>
-      <c r="AF28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>160</v>
-      </c>
-      <c r="AP28" t="n">
+      <c r="BM28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP28" t="n">
         <v>16</v>
       </c>
-      <c r="AQ28" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BI28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>150</v>
-      </c>
-      <c r="BM28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO28" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BP28" t="n">
-        <v>10</v>
-      </c>
       <c r="BQ28" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR28" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BS28" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BT28" t="n">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="BU28" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV28" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="BW28" t="n">
         <v>1.01</v>
       </c>
       <c r="BX28" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="BY28" t="n">
         <v>1.01</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G29" t="n">
         <v>2.42</v>
@@ -7739,7 +7739,7 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="O29" t="n">
         <v>1.02</v>
@@ -7748,7 +7748,7 @@
         <v>1.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="R29" t="n">
         <v>1.18</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -7960,226 +7960,226 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles 78 FC</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Villefranche Beaujolais</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.81</v>
+        <v>1.43</v>
       </c>
       <c r="G30" t="n">
-        <v>2.04</v>
+        <v>1.52</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="I30" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="K30" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="L30" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="M30" t="n">
         <v>1.05</v>
       </c>
       <c r="N30" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="O30" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="P30" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="R30" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="S30" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="T30" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="U30" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="V30" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="W30" t="n">
-        <v>1.94</v>
+        <v>2.92</v>
       </c>
       <c r="X30" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="Y30" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="Z30" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AA30" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI30" t="n">
         <v>120</v>
       </c>
-      <c r="AB30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC30" t="n">
+      <c r="AJ30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>150</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP30" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD30" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI30" t="n">
+      <c r="BQ30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>27</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>13</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>80</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX30" t="n">
         <v>75</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BI30" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BJ30" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL30" t="n">
-        <v>140</v>
-      </c>
-      <c r="BM30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BO30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP30" t="n">
-        <v>16</v>
-      </c>
-      <c r="BQ30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR30" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT30" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BU30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV30" t="n">
-        <v>44</v>
-      </c>
-      <c r="BW30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX30" t="n">
-        <v>55</v>
       </c>
       <c r="BY30" t="n">
         <v>1.01</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -8235,7 +8235,7 @@
         <v>2.44</v>
       </c>
       <c r="J31" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="K31" t="n">
         <v>4.8</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -8468,121 +8468,121 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chateauroux</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4.1</v>
+        <v>1.63</v>
       </c>
       <c r="G32" t="n">
-        <v>5</v>
+        <v>1.98</v>
       </c>
       <c r="H32" t="n">
-        <v>1.81</v>
+        <v>4.2</v>
       </c>
       <c r="I32" t="n">
-        <v>1.88</v>
+        <v>7</v>
       </c>
       <c r="J32" t="n">
         <v>3.85</v>
       </c>
       <c r="K32" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="L32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R32" t="n">
         <v>1.34</v>
       </c>
-      <c r="M32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N32" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P32" t="n">
+      <c r="S32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W32" t="n">
         <v>2.02</v>
       </c>
-      <c r="Q32" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V32" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X32" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA32" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE32" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AG32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH32" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI32" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM32" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP32" t="n">
         <v>1.01</v>
@@ -8639,55 +8639,55 @@
         <v>1.01</v>
       </c>
       <c r="BH32" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI32" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ32" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK32" t="n">
         <v>1.01</v>
       </c>
       <c r="BL32" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BM32" t="n">
         <v>1.01</v>
       </c>
       <c r="BN32" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BO32" t="n">
         <v>1.01</v>
       </c>
       <c r="BP32" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BQ32" t="n">
         <v>1.01</v>
       </c>
       <c r="BR32" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS32" t="n">
         <v>1.01</v>
       </c>
       <c r="BT32" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU32" t="n">
         <v>1.01</v>
       </c>
       <c r="BV32" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BW32" t="n">
         <v>1.01</v>
       </c>
       <c r="BX32" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY32" t="n">
         <v>1.01</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -8722,121 +8722,121 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Orleans</t>
+          <t>Chateauroux</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.63</v>
+        <v>4.1</v>
       </c>
       <c r="G33" t="n">
-        <v>1.98</v>
+        <v>4.9</v>
       </c>
       <c r="H33" t="n">
-        <v>4.2</v>
+        <v>1.81</v>
       </c>
       <c r="I33" t="n">
-        <v>7</v>
+        <v>1.88</v>
       </c>
       <c r="J33" t="n">
         <v>3.85</v>
       </c>
       <c r="K33" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M33" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N33" t="n">
-        <v>2.32</v>
+        <v>3.55</v>
       </c>
       <c r="O33" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="P33" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U33" t="n">
         <v>2.12</v>
       </c>
-      <c r="Q33" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.11</v>
-      </c>
       <c r="V33" t="n">
-        <v>1.16</v>
+        <v>2.12</v>
       </c>
       <c r="W33" t="n">
-        <v>2.02</v>
+        <v>1.25</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y33" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD33" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG33" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH33" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP33" t="n">
         <v>1.01</v>
@@ -8893,55 +8893,55 @@
         <v>1.01</v>
       </c>
       <c r="BH33" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI33" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ33" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK33" t="n">
         <v>1.01</v>
       </c>
       <c r="BL33" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM33" t="n">
         <v>1.01</v>
       </c>
       <c r="BN33" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BO33" t="n">
         <v>1.01</v>
       </c>
       <c r="BP33" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ33" t="n">
         <v>1.01</v>
       </c>
       <c r="BR33" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS33" t="n">
         <v>1.01</v>
       </c>
       <c r="BT33" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU33" t="n">
         <v>1.01</v>
       </c>
       <c r="BV33" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW33" t="n">
         <v>1.01</v>
       </c>
       <c r="BX33" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY33" t="n">
         <v>1.01</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -9009,22 +9009,22 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="O34" t="n">
         <v>1.24</v>
       </c>
       <c r="P34" t="n">
-        <v>1.96</v>
+        <v>1.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.72</v>
+        <v>1.24</v>
       </c>
       <c r="R34" t="n">
         <v>1.18</v>
       </c>
       <c r="S34" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="T34" t="n">
         <v>1.01</v>
@@ -9147,7 +9147,7 @@
         <v>1.01</v>
       </c>
       <c r="BH34" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI34" t="n">
         <v>2.52</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
         <v>1.92</v>
       </c>
       <c r="G35" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="H35" t="n">
         <v>3.55</v>
@@ -9254,7 +9254,7 @@
         <v>3.5</v>
       </c>
       <c r="K35" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="L35" t="n">
         <v>1.28</v>
@@ -9287,7 +9287,7 @@
         <v>2.18</v>
       </c>
       <c r="V35" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W35" t="n">
         <v>1.85</v>
@@ -9425,7 +9425,7 @@
         <v>4</v>
       </c>
       <c r="BP35" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="BQ35" t="n">
         <v>1.01</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -10004,16 +10004,16 @@
         <v>1.99</v>
       </c>
       <c r="G38" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H38" t="n">
         <v>3.05</v>
       </c>
       <c r="I38" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="J38" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="K38" t="n">
         <v>4.9</v>
@@ -10052,7 +10052,7 @@
         <v>1.37</v>
       </c>
       <c r="W38" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="X38" t="n">
         <v>40</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10509,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G40" t="n">
         <v>1.65</v>
@@ -10548,7 +10548,7 @@
         <v>1.67</v>
       </c>
       <c r="S40" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T40" t="n">
         <v>1.6</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -10784,7 +10784,7 @@
         <v>1.25</v>
       </c>
       <c r="M41" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N41" t="n">
         <v>5.1</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -11152,7 +11152,7 @@
         <v>4</v>
       </c>
       <c r="AY42" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AZ42" t="n">
         <v>13.5</v>
@@ -11170,7 +11170,7 @@
         <v>4.1</v>
       </c>
       <c r="BE42" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF42" t="n">
         <v>4</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -11274,16 +11274,16 @@
         <v>1.72</v>
       </c>
       <c r="G43" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H43" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I43" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="J43" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="K43" t="n">
         <v>4.6</v>
@@ -11292,10 +11292,10 @@
         <v>1.01</v>
       </c>
       <c r="M43" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N43" t="n">
-        <v>2.66</v>
+        <v>5.6</v>
       </c>
       <c r="O43" t="n">
         <v>1.18</v>
@@ -11310,49 +11310,49 @@
         <v>1.68</v>
       </c>
       <c r="S43" t="n">
-        <v>2.28</v>
+        <v>1.54</v>
       </c>
       <c r="T43" t="n">
         <v>1.49</v>
       </c>
       <c r="U43" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W43" t="n">
         <v>2.2</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W43" t="n">
-        <v>2.22</v>
       </c>
       <c r="X43" t="n">
         <v>34</v>
       </c>
       <c r="Y43" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z43" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA43" t="n">
         <v>1000</v>
       </c>
       <c r="AB43" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AC43" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AD43" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE43" t="n">
         <v>60</v>
       </c>
       <c r="AF43" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AG43" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH43" t="n">
         <v>21</v>
@@ -11364,7 +11364,7 @@
         <v>25</v>
       </c>
       <c r="AK43" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AL43" t="n">
         <v>32</v>
@@ -11373,65 +11373,65 @@
         <v>75</v>
       </c>
       <c r="AN43" t="n">
-        <v>120</v>
+        <v>970</v>
       </c>
       <c r="AO43" t="n">
         <v>42</v>
       </c>
       <c r="AP43" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ43" t="n">
         <v>2.32</v>
       </c>
-      <c r="AQ43" t="n">
+      <c r="AR43" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BB43" t="n">
         <v>2.3</v>
       </c>
-      <c r="AR43" t="n">
+      <c r="BC43" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG43" t="n">
         <v>2.02</v>
       </c>
-      <c r="AS43" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BF43" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BG43" t="n">
-        <v>2</v>
-      </c>
       <c r="BH43" t="n">
         <v>1000</v>
       </c>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -11549,28 +11549,28 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O44" t="n">
         <v>1.35</v>
       </c>
       <c r="P44" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="R44" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S44" t="n">
-        <v>2.08</v>
+        <v>2.56</v>
       </c>
       <c r="T44" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U44" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V44" t="n">
         <v>1.42</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -11803,7 +11803,7 @@
         <v>1.02</v>
       </c>
       <c r="N45" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O45" t="n">
         <v>1.17</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -12063,22 +12063,22 @@
         <v>1.14</v>
       </c>
       <c r="P46" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="R46" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="S46" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="T46" t="n">
         <v>1.8</v>
       </c>
       <c r="U46" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="V46" t="n">
         <v>1.09</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -12290,7 +12290,7 @@
         <v>1.87</v>
       </c>
       <c r="G47" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="H47" t="n">
         <v>4.1</v>
@@ -12311,16 +12311,16 @@
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>1.83</v>
+        <v>2.64</v>
       </c>
       <c r="O47" t="n">
         <v>1.33</v>
       </c>
       <c r="P47" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R47" t="n">
         <v>1.24</v>
@@ -12329,16 +12329,16 @@
         <v>3.2</v>
       </c>
       <c r="T47" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U47" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V47" t="n">
         <v>1.25</v>
       </c>
       <c r="W47" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="X47" t="n">
         <v>1000</v>
@@ -12510,14 +12510,14 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -12532,175 +12532,175 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Partick</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dunfermline</t>
+          <t>Drogheda</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="G48" t="n">
-        <v>2.06</v>
+        <v>1.63</v>
       </c>
       <c r="H48" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I48" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J48" t="n">
         <v>4.1</v>
       </c>
-      <c r="I48" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J48" t="n">
-        <v>3.5</v>
-      </c>
       <c r="K48" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="L48" t="n">
         <v>1.01</v>
       </c>
       <c r="M48" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N48" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="O48" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="P48" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="Q48" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T48" t="n">
         <v>2</v>
       </c>
-      <c r="R48" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S48" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T48" t="n">
-        <v>1.01</v>
-      </c>
       <c r="U48" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V48" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="W48" t="n">
-        <v>1.95</v>
+        <v>2.58</v>
       </c>
       <c r="X48" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y48" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z48" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AA48" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB48" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AC48" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD48" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ48" t="n">
         <v>18.5</v>
       </c>
-      <c r="AE48" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>24</v>
-      </c>
       <c r="AK48" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL48" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM48" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN48" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AO48" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP48" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BB48" t="n">
         <v>10</v>
       </c>
-      <c r="AQ48" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB48" t="n">
-        <v>17</v>
-      </c>
       <c r="BC48" t="n">
-        <v>16.5</v>
+        <v>1.39</v>
       </c>
       <c r="BD48" t="n">
-        <v>7</v>
+        <v>1.49</v>
       </c>
       <c r="BE48" t="n">
-        <v>7.8</v>
+        <v>1.49</v>
       </c>
       <c r="BF48" t="n">
-        <v>11.5</v>
+        <v>1.49</v>
       </c>
       <c r="BG48" t="n">
-        <v>9</v>
+        <v>1.49</v>
       </c>
       <c r="BH48" t="n">
         <v>1000</v>
@@ -12764,14 +12764,14 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -12786,175 +12786,175 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Partick</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Drogheda</t>
+          <t>Dunfermline</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="G49" t="n">
-        <v>1.63</v>
+        <v>2.04</v>
       </c>
       <c r="H49" t="n">
-        <v>6.8</v>
+        <v>4.1</v>
       </c>
       <c r="I49" t="n">
-        <v>9.6</v>
+        <v>4.7</v>
       </c>
       <c r="J49" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K49" t="n">
         <v>4.1</v>
       </c>
-      <c r="K49" t="n">
-        <v>4.8</v>
-      </c>
       <c r="L49" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="M49" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N49" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="O49" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="P49" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="R49" t="n">
         <v>1.32</v>
       </c>
       <c r="S49" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="T49" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U49" t="n">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="V49" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="W49" t="n">
-        <v>2.58</v>
+        <v>1.96</v>
       </c>
       <c r="X49" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y49" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="AA49" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB49" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AC49" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD49" t="n">
-        <v>38</v>
+        <v>18.5</v>
       </c>
       <c r="AE49" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF49" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF49" t="n">
         <v>11.5</v>
       </c>
-      <c r="AG49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BA49" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BB49" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC49" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BD49" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BE49" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BF49" t="n">
-        <v>1.48</v>
-      </c>
       <c r="BG49" t="n">
-        <v>1.48</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH49" t="n">
         <v>1000</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -13049,10 +13049,10 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G50" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="H50" t="n">
         <v>2.3</v>
@@ -13070,13 +13070,13 @@
         <v>1.01</v>
       </c>
       <c r="M50" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N50" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="O50" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P50" t="n">
         <v>1.97</v>
@@ -13085,130 +13085,130 @@
         <v>1.78</v>
       </c>
       <c r="R50" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S50" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="T50" t="n">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="U50" t="n">
-        <v>1.86</v>
+        <v>2.22</v>
       </c>
       <c r="V50" t="n">
         <v>1.66</v>
       </c>
       <c r="W50" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="X50" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y50" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Z50" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AA50" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL50" t="n">
         <v>46</v>
       </c>
-      <c r="AB50" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>60</v>
-      </c>
       <c r="AM50" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN50" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO50" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.82</v>
+        <v>4.2</v>
       </c>
       <c r="AQ50" t="n">
-        <v>2.66</v>
+        <v>5.2</v>
       </c>
       <c r="AR50" t="n">
-        <v>11</v>
+        <v>5.9</v>
       </c>
       <c r="AS50" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW50" t="n">
         <v>3.1</v>
       </c>
-      <c r="AT50" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>3.05</v>
-      </c>
       <c r="AX50" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AY50" t="n">
-        <v>9.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AZ50" t="n">
-        <v>2.86</v>
+        <v>4.1</v>
       </c>
       <c r="BA50" t="n">
-        <v>3.15</v>
+        <v>2.74</v>
       </c>
       <c r="BB50" t="n">
-        <v>3.2</v>
+        <v>2.18</v>
       </c>
       <c r="BC50" t="n">
-        <v>23</v>
+        <v>2.72</v>
       </c>
       <c r="BD50" t="n">
-        <v>3.15</v>
+        <v>2.18</v>
       </c>
       <c r="BE50" t="n">
-        <v>3.35</v>
+        <v>5.2</v>
       </c>
       <c r="BF50" t="n">
-        <v>3.35</v>
+        <v>2.16</v>
       </c>
       <c r="BG50" t="n">
-        <v>3.35</v>
+        <v>13.5</v>
       </c>
       <c r="BH50" t="n">
         <v>1000</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -13312,7 +13312,7 @@
         <v>1.67</v>
       </c>
       <c r="I51" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="J51" t="n">
         <v>3.8</v>
@@ -13327,31 +13327,31 @@
         <v>1.01</v>
       </c>
       <c r="N51" t="n">
-        <v>1.94</v>
+        <v>2.76</v>
       </c>
       <c r="O51" t="n">
         <v>1.28</v>
       </c>
       <c r="P51" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q51" t="n">
         <v>1.76</v>
       </c>
       <c r="R51" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S51" t="n">
-        <v>1.78</v>
+        <v>2.34</v>
       </c>
       <c r="T51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V51" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="W51" t="n">
         <v>1.16</v>
@@ -13526,14 +13526,14 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -13548,226 +13548,226 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Oud-Heverlee Leuven</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Antwerp</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.82</v>
+        <v>2.32</v>
       </c>
       <c r="G52" t="n">
-        <v>3.25</v>
+        <v>2.66</v>
       </c>
       <c r="H52" t="n">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="I52" t="n">
-        <v>2.74</v>
+        <v>3.85</v>
       </c>
       <c r="J52" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="K52" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="L52" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N52" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O52" t="n">
         <v>1.38</v>
       </c>
-      <c r="M52" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N52" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="O52" t="n">
-        <v>1.29</v>
-      </c>
       <c r="P52" t="n">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="R52" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="S52" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="T52" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="U52" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="V52" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="W52" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="X52" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Y52" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Z52" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA52" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AB52" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG52" t="n">
         <v>13.5</v>
       </c>
-      <c r="AC52" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AH52" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI52" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AJ52" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AK52" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL52" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM52" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN52" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO52" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP52" t="n">
-        <v>2.42</v>
+        <v>9</v>
       </c>
       <c r="AQ52" t="n">
-        <v>2.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR52" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="AS52" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="AT52" t="n">
-        <v>2.38</v>
+        <v>7.2</v>
       </c>
       <c r="AU52" t="n">
-        <v>2.2</v>
+        <v>5.9</v>
       </c>
       <c r="AV52" t="n">
-        <v>2.4</v>
+        <v>11</v>
       </c>
       <c r="AW52" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="AX52" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="AY52" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ52" t="n">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="BA52" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="BB52" t="n">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="BC52" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BD52" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="BE52" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="BF52" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="BG52" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="BH52" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI52" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BJ52" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK52" t="n">
         <v>1.01</v>
       </c>
       <c r="BL52" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM52" t="n">
         <v>1.01</v>
       </c>
       <c r="BN52" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO52" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP52" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ52" t="n">
         <v>1.01</v>
       </c>
       <c r="BR52" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS52" t="n">
         <v>1.01</v>
       </c>
       <c r="BT52" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU52" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV52" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW52" t="n">
         <v>1.01</v>
       </c>
       <c r="BX52" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY52" t="n">
         <v>1.01</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -13814,13 +13814,13 @@
         <v>1.93</v>
       </c>
       <c r="G53" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="H53" t="n">
         <v>3.9</v>
       </c>
       <c r="I53" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="J53" t="n">
         <v>3.1</v>
@@ -13835,7 +13835,7 @@
         <v>1.07</v>
       </c>
       <c r="N53" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O53" t="n">
         <v>1.33</v>
@@ -13982,13 +13982,13 @@
         <v>12</v>
       </c>
       <c r="BK53" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BL53" t="n">
         <v>160</v>
       </c>
       <c r="BM53" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BN53" t="n">
         <v>5.6</v>
@@ -14000,13 +14000,13 @@
         <v>18</v>
       </c>
       <c r="BQ53" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BR53" t="n">
         <v>36</v>
       </c>
       <c r="BS53" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BT53" t="n">
         <v>9</v>
@@ -14018,13 +14018,13 @@
         <v>44</v>
       </c>
       <c r="BW53" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BX53" t="n">
         <v>60</v>
       </c>
       <c r="BY53" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BZ53" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -14083,13 +14083,13 @@
         <v>5.7</v>
       </c>
       <c r="L54" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M54" t="n">
         <v>1.01</v>
       </c>
       <c r="N54" t="n">
-        <v>1.61</v>
+        <v>2.34</v>
       </c>
       <c r="O54" t="n">
         <v>1.35</v>
@@ -14107,10 +14107,10 @@
         <v>3.25</v>
       </c>
       <c r="T54" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U54" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V54" t="n">
         <v>1.5</v>
@@ -14288,14 +14288,14 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Belgian Pro League</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -14310,226 +14310,226 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Oud-Heverlee Leuven</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Antwerp</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.32</v>
+        <v>2.82</v>
       </c>
       <c r="G55" t="n">
-        <v>2.66</v>
+        <v>3.25</v>
       </c>
       <c r="H55" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I55" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J55" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N55" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S55" t="n">
         <v>3.1</v>
       </c>
-      <c r="I55" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="J55" t="n">
+      <c r="T55" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X55" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS55" t="n">
         <v>3.1</v>
       </c>
-      <c r="K55" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L55" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M55" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N55" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O55" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P55" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S55" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T55" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X55" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AT55" t="n">
-        <v>7.2</v>
+        <v>2.68</v>
       </c>
       <c r="AU55" t="n">
-        <v>5.9</v>
+        <v>2.44</v>
       </c>
       <c r="AV55" t="n">
-        <v>11</v>
+        <v>2.72</v>
       </c>
       <c r="AW55" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AX55" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AY55" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BA55" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BC55" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BD55" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BG55" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BH55" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI55" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BJ55" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK55" t="n">
         <v>1.01</v>
       </c>
       <c r="BL55" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="BM55" t="n">
         <v>1.01</v>
       </c>
       <c r="BN55" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO55" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP55" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ55" t="n">
         <v>1.01</v>
       </c>
       <c r="BR55" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS55" t="n">
         <v>1.01</v>
       </c>
       <c r="BT55" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU55" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BV55" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW55" t="n">
         <v>1.01</v>
       </c>
       <c r="BX55" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY55" t="n">
         <v>1.01</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -14576,115 +14576,115 @@
         <v>2.3</v>
       </c>
       <c r="G56" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H56" t="n">
         <v>3.15</v>
       </c>
       <c r="I56" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="J56" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K56" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="L56" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M56" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N56" t="n">
-        <v>1.63</v>
+        <v>3.1</v>
       </c>
       <c r="O56" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S56" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V56" t="n">
         <v>1.37</v>
       </c>
-      <c r="P56" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S56" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T56" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1.34</v>
-      </c>
       <c r="W56" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X56" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y56" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z56" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA56" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB56" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC56" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD56" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE56" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF56" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG56" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH56" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI56" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ56" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK56" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL56" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM56" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN56" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO56" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR56" t="n">
         <v>1.01</v>
@@ -14693,25 +14693,25 @@
         <v>1.01</v>
       </c>
       <c r="AT56" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU56" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AV56" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW56" t="n">
         <v>1.01</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ56" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA56" t="n">
         <v>1.01</v>
@@ -14735,55 +14735,55 @@
         <v>1.01</v>
       </c>
       <c r="BH56" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI56" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BJ56" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK56" t="n">
         <v>1.01</v>
       </c>
       <c r="BL56" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BM56" t="n">
         <v>1.01</v>
       </c>
       <c r="BN56" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO56" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP56" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ56" t="n">
         <v>1.01</v>
       </c>
       <c r="BR56" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS56" t="n">
         <v>1.01</v>
       </c>
       <c r="BT56" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU56" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV56" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW56" t="n">
         <v>1.01</v>
       </c>
       <c r="BX56" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY56" t="n">
         <v>1.01</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -14827,28 +14827,28 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G57" t="n">
         <v>3.1</v>
       </c>
       <c r="H57" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I57" t="n">
         <v>2.38</v>
       </c>
       <c r="J57" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K57" t="n">
         <v>4</v>
-      </c>
-      <c r="K57" t="n">
-        <v>4.1</v>
       </c>
       <c r="L57" t="n">
         <v>1.29</v>
       </c>
       <c r="M57" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N57" t="n">
         <v>6</v>
@@ -14875,7 +14875,7 @@
         <v>2.8</v>
       </c>
       <c r="V57" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W57" t="n">
         <v>1.47</v>
@@ -14890,13 +14890,13 @@
         <v>18.5</v>
       </c>
       <c r="AA57" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB57" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC57" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD57" t="n">
         <v>11.5</v>
@@ -14920,7 +14920,7 @@
         <v>50</v>
       </c>
       <c r="AK57" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL57" t="n">
         <v>32</v>
@@ -14932,7 +14932,7 @@
         <v>17.5</v>
       </c>
       <c r="AO57" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AP57" t="n">
         <v>22</v>
@@ -14965,13 +14965,13 @@
         <v>12.5</v>
       </c>
       <c r="AZ57" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA57" t="n">
         <v>25</v>
       </c>
       <c r="BB57" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BC57" t="n">
         <v>26</v>
@@ -14980,13 +14980,13 @@
         <v>29</v>
       </c>
       <c r="BE57" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BF57" t="n">
         <v>16</v>
       </c>
       <c r="BG57" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH57" t="n">
         <v>5.3</v>
@@ -14998,13 +14998,13 @@
         <v>10.5</v>
       </c>
       <c r="BK57" t="n">
-        <v>6.2</v>
+        <v>3.4</v>
       </c>
       <c r="BL57" t="n">
         <v>85</v>
       </c>
       <c r="BM57" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BN57" t="n">
         <v>8</v>
@@ -15022,7 +15022,7 @@
         <v>32</v>
       </c>
       <c r="BS57" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BT57" t="n">
         <v>6.8</v>
@@ -15034,23 +15034,23 @@
         <v>18.5</v>
       </c>
       <c r="BW57" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BX57" t="n">
         <v>28</v>
       </c>
       <c r="BY57" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BZ57" t="n">
         <v>18.5</v>
       </c>
       <c r="CA57" t="n">
-        <v>11</v>
+        <v>3.75</v>
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -15090,7 +15090,7 @@
         <v>5.3</v>
       </c>
       <c r="I58" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J58" t="n">
         <v>4.3</v>
@@ -15102,10 +15102,10 @@
         <v>1.01</v>
       </c>
       <c r="M58" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N58" t="n">
-        <v>2.46</v>
+        <v>5.2</v>
       </c>
       <c r="O58" t="n">
         <v>1.2</v>
@@ -15117,130 +15117,130 @@
         <v>1.61</v>
       </c>
       <c r="R58" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="S58" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="T58" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="U58" t="n">
         <v>2.3</v>
       </c>
       <c r="V58" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W58" t="n">
         <v>2.36</v>
       </c>
       <c r="X58" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="Y58" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Z58" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE58" t="n">
         <v>65</v>
       </c>
-      <c r="AA58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>70</v>
-      </c>
       <c r="AF58" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG58" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH58" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI58" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ58" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AK58" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AL58" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AM58" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AN58" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AO58" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP58" t="n">
-        <v>2.32</v>
+        <v>7.4</v>
       </c>
       <c r="AQ58" t="n">
-        <v>2.32</v>
+        <v>7.4</v>
       </c>
       <c r="AR58" t="n">
-        <v>2.42</v>
+        <v>8.6</v>
       </c>
       <c r="AS58" t="n">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="AT58" t="n">
-        <v>2.12</v>
+        <v>10</v>
       </c>
       <c r="AU58" t="n">
-        <v>2.08</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV58" t="n">
-        <v>2.26</v>
+        <v>7.2</v>
       </c>
       <c r="AW58" t="n">
-        <v>2.42</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX58" t="n">
-        <v>2.14</v>
+        <v>10.5</v>
       </c>
       <c r="AY58" t="n">
-        <v>2.08</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ58" t="n">
-        <v>2.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA58" t="n">
-        <v>2.42</v>
+        <v>9</v>
       </c>
       <c r="BB58" t="n">
-        <v>2.22</v>
+        <v>15</v>
       </c>
       <c r="BC58" t="n">
-        <v>2.22</v>
+        <v>14</v>
       </c>
       <c r="BD58" t="n">
-        <v>19.5</v>
+        <v>7.6</v>
       </c>
       <c r="BE58" t="n">
-        <v>2.44</v>
+        <v>9.4</v>
       </c>
       <c r="BF58" t="n">
-        <v>2.5</v>
+        <v>6.4</v>
       </c>
       <c r="BG58" t="n">
-        <v>2.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH58" t="n">
         <v>1000</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -15335,19 +15335,19 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G59" t="n">
         <v>1000</v>
       </c>
       <c r="H59" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I59" t="n">
         <v>1000</v>
       </c>
       <c r="J59" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K59" t="n">
         <v>440</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -15589,19 +15589,19 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G60" t="n">
         <v>1000</v>
       </c>
       <c r="H60" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I60" t="n">
         <v>1000</v>
       </c>
       <c r="J60" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K60" t="n">
         <v>410</v>
@@ -15619,7 +15619,7 @@
         <v>1.07</v>
       </c>
       <c r="P60" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q60" t="n">
         <v>1.07</v>
@@ -15631,10 +15631,10 @@
         <v>1.07</v>
       </c>
       <c r="T60" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U60" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V60" t="n">
         <v>1.01</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -15834,12 +15834,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>Nacional (Par)</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -15861,28 +15861,28 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N61" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O61" t="n">
         <v>1.46</v>
-      </c>
-      <c r="M61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N61" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="O61" t="n">
-        <v>1.4</v>
       </c>
       <c r="P61" t="n">
         <v>1.24</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="R61" t="n">
         <v>1.18</v>
       </c>
       <c r="S61" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T61" t="n">
         <v>1.01</v>
@@ -15951,52 +15951,52 @@
         <v>1000</v>
       </c>
       <c r="AP61" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ61" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AR61" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AS61" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AT61" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU61" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV61" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AW61" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX61" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY61" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ61" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA61" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BB61" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BC61" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BD61" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE61" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF61" t="n">
         <v>1.01</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Nacional (Par)</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -16115,34 +16115,34 @@
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M62" t="n">
         <v>1.01</v>
       </c>
       <c r="N62" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O62" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="P62" t="n">
         <v>1.24</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="R62" t="n">
         <v>1.18</v>
       </c>
       <c r="S62" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="T62" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U62" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V62" t="n">
         <v>1.01</v>
@@ -16205,52 +16205,52 @@
         <v>1000</v>
       </c>
       <c r="AP62" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ62" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AR62" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AS62" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AT62" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AU62" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV62" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW62" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AX62" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AY62" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ62" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA62" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB62" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BC62" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BD62" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BE62" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF62" t="n">
         <v>1.01</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-05-13 17:39:06</t>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>
@@ -16351,16 +16351,16 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2.72</v>
+        <v>2.22</v>
       </c>
       <c r="G63" t="n">
         <v>3.65</v>
       </c>
       <c r="H63" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="I63" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J63" t="n">
         <v>3</v>
@@ -16369,13 +16369,13 @@
         <v>110</v>
       </c>
       <c r="L63" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M63" t="n">
         <v>1.01</v>
       </c>
       <c r="N63" t="n">
-        <v>3.3</v>
+        <v>1.73</v>
       </c>
       <c r="O63" t="n">
         <v>1.31</v>
@@ -16399,7 +16399,7 @@
         <v>1.01</v>
       </c>
       <c r="V63" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W63" t="n">
         <v>1.37</v>
@@ -16459,122 +16459,630 @@
         <v>1000</v>
       </c>
       <c r="AP63" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ63" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR63" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB63" t="inlineStr">
+        <is>
+          <t>2026-05-13 19:57:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LDU</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Tecnico Universitario</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H64" t="n">
+        <v>7</v>
+      </c>
+      <c r="I64" t="n">
+        <v>8</v>
+      </c>
+      <c r="J64" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K64" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N64" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>2</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W64" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="X64" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK64" t="n">
         <v>25</v>
       </c>
-      <c r="AT63" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU63" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV63" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW63" t="n">
+      <c r="AL64" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ64" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR64" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AS64" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT64" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AU64" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AV64" t="n">
         <v>19</v>
       </c>
-      <c r="AX63" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY63" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ63" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA63" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB63" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC63" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD63" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE63" t="n">
-        <v>40</v>
-      </c>
-      <c r="BF63" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG63" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI63" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK63" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM63" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO63" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ63" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS63" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU63" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW63" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY63" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA63" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB63" t="inlineStr">
-        <is>
-          <t>2026-05-13 17:39:06</t>
+      <c r="AW64" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AX64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY64" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AZ64" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BA64" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB64" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC64" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BD64" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BE64" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BF64" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BG64" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI64" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK64" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM64" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO64" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ64" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS64" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU64" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW64" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY64" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA64" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB64" t="inlineStr">
+        <is>
+          <t>2026-05-13 19:57:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Venezuelan Primera Division</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Deportivo La Guaira</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Universidad de Venezuela</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N65" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB65" t="inlineStr">
+        <is>
+          <t>2026-05-13 19:57:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB65"/>
+  <dimension ref="A1:CB66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="G2" t="n">
         <v>6.4</v>
       </c>
       <c r="H2" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="I2" t="n">
         <v>1.85</v>
@@ -872,7 +872,7 @@
         <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -896,7 +896,7 @@
         <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>2.54</v>
+        <v>2.18</v>
       </c>
       <c r="T2" t="n">
         <v>1.61</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -1135,19 +1135,19 @@
         <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O3" t="n">
         <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S3" t="n">
         <v>2.62</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.25</v>
@@ -1389,13 +1389,13 @@
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O4" t="n">
         <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="Q4" t="n">
         <v>1.53</v>
@@ -1458,7 +1458,7 @@
         <v>28</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AL4" t="n">
         <v>30</v>
@@ -1473,16 +1473,16 @@
         <v>28</v>
       </c>
       <c r="AP4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ4" t="n">
         <v>18</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT4" t="n">
         <v>12.5</v>
@@ -1494,7 +1494,7 @@
         <v>14</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX4" t="n">
         <v>14</v>
@@ -1506,19 +1506,19 @@
         <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC4" t="n">
         <v>16</v>
       </c>
       <c r="BD4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF4" t="n">
         <v>7</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="G5" t="n">
         <v>6.6</v>
@@ -1634,16 +1634,16 @@
         <v>3.95</v>
       </c>
       <c r="K5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O5" t="n">
         <v>1.28</v>
@@ -1652,13 +1652,13 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R5" t="n">
         <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T5" t="n">
         <v>1.82</v>
@@ -1673,10 +1673,10 @@
         <v>1.18</v>
       </c>
       <c r="X5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y5" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="Z5" t="n">
         <v>12.5</v>
@@ -1688,13 +1688,13 @@
         <v>25</v>
       </c>
       <c r="AC5" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AD5" t="n">
         <v>12</v>
       </c>
       <c r="AE5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AF5" t="n">
         <v>60</v>
@@ -1751,7 +1751,7 @@
         <v>14.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AY5" t="n">
         <v>19</v>
@@ -1760,22 +1760,22 @@
         <v>17.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BG5" t="n">
         <v>7.2</v>
@@ -1784,7 +1784,7 @@
         <v>4.3</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BJ5" t="n">
         <v>12.5</v>
@@ -1793,7 +1793,7 @@
         <v>1.01</v>
       </c>
       <c r="BL5" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="BM5" t="n">
         <v>1.01</v>
@@ -1817,7 +1817,7 @@
         <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BU5" t="n">
         <v>3.35</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -1876,13 +1876,13 @@
         <v>1.66</v>
       </c>
       <c r="G6" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="H6" t="n">
         <v>5.3</v>
       </c>
       <c r="I6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J6" t="n">
         <v>3.95</v>
@@ -1891,10 +1891,10 @@
         <v>4.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
         <v>4</v>
@@ -1903,7 +1903,7 @@
         <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q6" t="n">
         <v>1.71</v>
@@ -1921,10 +1921,10 @@
         <v>2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W6" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="X6" t="n">
         <v>20</v>
@@ -1933,28 +1933,28 @@
         <v>24</v>
       </c>
       <c r="Z6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AA6" t="n">
         <v>180</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC6" t="n">
         <v>11</v>
       </c>
       <c r="AD6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE6" t="n">
         <v>90</v>
       </c>
       <c r="AF6" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH6" t="n">
         <v>22</v>
@@ -1963,13 +1963,13 @@
         <v>90</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AK6" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM6" t="n">
         <v>140</v>
@@ -1987,10 +1987,10 @@
         <v>16.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="AT6" t="n">
         <v>7.6</v>
@@ -2002,7 +2002,7 @@
         <v>18.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX6" t="n">
         <v>9</v>
@@ -2014,7 +2014,7 @@
         <v>17.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB6" t="n">
         <v>12.5</v>
@@ -2023,16 +2023,16 @@
         <v>15</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BF6" t="n">
         <v>7.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BH6" t="n">
         <v>4.3</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="G7" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H7" t="n">
         <v>6.8</v>
@@ -2142,7 +2142,7 @@
         <v>5.3</v>
       </c>
       <c r="K7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L7" t="n">
         <v>1.22</v>
@@ -2151,52 +2151,52 @@
         <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P7" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="R7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S7" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="V7" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W7" t="n">
         <v>3.05</v>
       </c>
       <c r="X7" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Y7" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Z7" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
         <v>230</v>
       </c>
       <c r="AB7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC7" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AD7" t="n">
         <v>34</v>
@@ -2205,22 +2205,22 @@
         <v>110</v>
       </c>
       <c r="AF7" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AG7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
         <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AL7" t="n">
         <v>34</v>
@@ -2232,19 +2232,19 @@
         <v>4.9</v>
       </c>
       <c r="AO7" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.5</v>
+        <v>21</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.7</v>
+        <v>32</v>
       </c>
       <c r="AS7" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="AT7" t="n">
         <v>10.5</v>
@@ -2253,40 +2253,40 @@
         <v>10</v>
       </c>
       <c r="AV7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.8</v>
+        <v>36</v>
       </c>
       <c r="AX7" t="n">
         <v>9.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.7</v>
+        <v>32</v>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BD7" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.8</v>
+        <v>36</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.8</v>
+        <v>36</v>
       </c>
       <c r="BH7" t="n">
         <v>5.8</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
         <v>1.81</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I8" t="n">
         <v>6</v>
@@ -2411,13 +2411,13 @@
         <v>1.29</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q8" t="n">
         <v>1.87</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
         <v>3.2</v>
@@ -2435,7 +2435,7 @@
         <v>2.22</v>
       </c>
       <c r="X8" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="Y8" t="n">
         <v>23</v>
@@ -2468,7 +2468,7 @@
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ8" t="n">
         <v>23</v>
@@ -2495,10 +2495,10 @@
         <v>15.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AT8" t="n">
         <v>7.8</v>
@@ -2510,7 +2510,7 @@
         <v>17.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AX8" t="n">
         <v>9</v>
@@ -2522,7 +2522,7 @@
         <v>17</v>
       </c>
       <c r="BA8" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BB8" t="n">
         <v>15.5</v>
@@ -2531,22 +2531,22 @@
         <v>15.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF8" t="n">
         <v>8</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH8" t="n">
         <v>4.2</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BJ8" t="n">
         <v>12</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -2892,19 +2892,19 @@
         <v>1.04</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H10" t="n">
         <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J10" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
         <v>4.3</v>
       </c>
       <c r="H11" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I11" t="n">
         <v>2.26</v>
@@ -3158,7 +3158,7 @@
         <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L11" t="n">
         <v>1.32</v>
@@ -3176,7 +3176,7 @@
         <v>1.97</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R11" t="n">
         <v>1.37</v>
@@ -3212,7 +3212,7 @@
         <v>970</v>
       </c>
       <c r="AC11" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD11" t="n">
         <v>970</v>
@@ -3260,7 +3260,7 @@
         <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AT11" t="n">
         <v>1.01</v>
@@ -3359,14 +3359,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CA11" t="n">
         <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
         <v>1.08</v>
       </c>
       <c r="S13" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="T13" t="n">
         <v>1.11</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -3908,13 +3908,13 @@
         <v>1.02</v>
       </c>
       <c r="G14" t="n">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H14" t="n">
         <v>1.02</v>
       </c>
       <c r="I14" t="n">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J14" t="n">
         <v>1.04</v>
@@ -3929,28 +3929,28 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O14" t="n">
         <v>1.15</v>
       </c>
       <c r="P14" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="R14" t="n">
         <v>1.08</v>
       </c>
       <c r="S14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
         <v>1.01</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>1.04</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H15" t="n">
         <v>1.04</v>
@@ -4171,10 +4171,10 @@
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -4201,10 +4201,10 @@
         <v>3.5</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
         <v>1.01</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -4942,7 +4942,7 @@
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N18" t="n">
         <v>4.9</v>
@@ -4960,13 +4960,13 @@
         <v>1.53</v>
       </c>
       <c r="S18" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V18" t="n">
         <v>1.96</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -5178,13 +5178,13 @@
         <v>1.04</v>
       </c>
       <c r="G19" t="n">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H19" t="n">
         <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J19" t="n">
         <v>1.04</v>
@@ -5199,7 +5199,7 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O19" t="n">
         <v>1.1</v>
@@ -5217,10 +5217,10 @@
         <v>1.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
         <v>2.24</v>
       </c>
       <c r="J20" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="K20" t="n">
         <v>4.5</v>
@@ -5462,13 +5462,13 @@
         <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="R20" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="S20" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="T20" t="n">
         <v>1.49</v>
@@ -5480,7 +5480,7 @@
         <v>1.8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="X20" t="n">
         <v>28</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
         <v>3.5</v>
       </c>
       <c r="K21" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -5719,16 +5719,16 @@
         <v>1.81</v>
       </c>
       <c r="R21" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="S21" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V21" t="n">
         <v>1.53</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
         <v>4.2</v>
       </c>
       <c r="L23" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="M23" t="n">
         <v>1.08</v>
@@ -6230,10 +6230,10 @@
         <v>1.28</v>
       </c>
       <c r="S23" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T23" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="U23" t="n">
         <v>1.87</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
         <v>1.53</v>
       </c>
       <c r="R24" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
         <v>2.32</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -6699,58 +6699,58 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5.8</v>
+        <v>3.05</v>
       </c>
       <c r="G25" t="n">
-        <v>10.5</v>
+        <v>990</v>
       </c>
       <c r="H25" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="I25" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="J25" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="K25" t="n">
-        <v>6</v>
+        <v>950</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M25" t="n">
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.92</v>
+        <v>3.35</v>
       </c>
       <c r="O25" t="n">
         <v>1.27</v>
       </c>
       <c r="P25" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q25" t="n">
         <v>1.86</v>
       </c>
       <c r="R25" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S25" t="n">
-        <v>1.86</v>
+        <v>2.86</v>
       </c>
       <c r="T25" t="n">
-        <v>1.82</v>
+        <v>1.11</v>
       </c>
       <c r="U25" t="n">
-        <v>1.86</v>
+        <v>1.11</v>
       </c>
       <c r="V25" t="n">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
       <c r="W25" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
         <v>970</v>
@@ -6759,7 +6759,7 @@
         <v>970</v>
       </c>
       <c r="Z25" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AA25" t="n">
         <v>970</v>
@@ -6774,16 +6774,16 @@
         <v>970</v>
       </c>
       <c r="AE25" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AF25" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AG25" t="n">
         <v>34</v>
       </c>
       <c r="AH25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI25" t="n">
         <v>48</v>
@@ -6804,7 +6804,7 @@
         <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AP25" t="n">
         <v>1.01</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -6953,16 +6953,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="G26" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="I26" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="J26" t="n">
         <v>4.2</v>
@@ -6998,13 +6998,13 @@
         <v>1.38</v>
       </c>
       <c r="U26" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="V26" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="W26" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X26" t="n">
         <v>34</v>
@@ -7019,7 +7019,7 @@
         <v>27</v>
       </c>
       <c r="AB26" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AC26" t="n">
         <v>12</v>
@@ -7031,7 +7031,7 @@
         <v>970</v>
       </c>
       <c r="AF26" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AG26" t="n">
         <v>970</v>
@@ -7055,64 +7055,64 @@
         <v>46</v>
       </c>
       <c r="AN26" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AO26" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AP26" t="n">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="AQ26" t="n">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="AR26" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="AS26" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="AT26" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU26" t="n">
         <v>10</v>
       </c>
       <c r="AV26" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="AW26" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="AX26" t="n">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AY26" t="n">
         <v>11</v>
       </c>
       <c r="AZ26" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="BB26" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BC26" t="n">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BD26" t="n">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BE26" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BF26" t="n">
         <v>12.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="BH26" t="n">
         <v>1000</v>
@@ -7176,14 +7176,14 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7198,229 +7198,229 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Arges Pitesti</t>
+          <t>Versailles 78 FC</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rapid Bucharest</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.32</v>
+        <v>1.43</v>
       </c>
       <c r="G27" t="n">
-        <v>3.2</v>
+        <v>1.52</v>
       </c>
       <c r="H27" t="n">
-        <v>2.48</v>
+        <v>6.8</v>
       </c>
       <c r="I27" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>2.96</v>
+        <v>4.1</v>
       </c>
       <c r="K27" t="n">
-        <v>100</v>
+        <v>5.4</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P27" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH27" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BI27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ27" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL27" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="BM27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN27" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BO27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP27" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BQ27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR27" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BS27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT27" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BU27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV27" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BW27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX27" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BY27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ27" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -7461,10 +7461,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="G28" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H28" t="n">
         <v>4</v>
@@ -7479,7 +7479,7 @@
         <v>4.2</v>
       </c>
       <c r="L28" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="M28" t="n">
         <v>1.06</v>
@@ -7491,7 +7491,7 @@
         <v>1.29</v>
       </c>
       <c r="P28" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q28" t="n">
         <v>1.71</v>
@@ -7512,7 +7512,7 @@
         <v>1.25</v>
       </c>
       <c r="W28" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="X28" t="n">
         <v>19.5</v>
@@ -7632,49 +7632,49 @@
         <v>12</v>
       </c>
       <c r="BK28" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BL28" t="n">
         <v>140</v>
       </c>
       <c r="BM28" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BN28" t="n">
         <v>5.5</v>
       </c>
       <c r="BO28" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BP28" t="n">
         <v>16</v>
       </c>
       <c r="BQ28" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BR28" t="n">
         <v>32</v>
       </c>
       <c r="BS28" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BT28" t="n">
         <v>9.4</v>
       </c>
       <c r="BU28" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BV28" t="n">
         <v>44</v>
       </c>
       <c r="BW28" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BX28" t="n">
         <v>55</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BZ28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
         <v>2.42</v>
       </c>
       <c r="O29" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="P29" t="n">
         <v>1.5</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7960,229 +7960,229 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Versailles 78 FC</t>
+          <t>Arges Pitesti</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rapid Bucharest</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.43</v>
+        <v>2.32</v>
       </c>
       <c r="G30" t="n">
-        <v>1.52</v>
+        <v>3.2</v>
       </c>
       <c r="H30" t="n">
-        <v>6.8</v>
+        <v>2.48</v>
       </c>
       <c r="I30" t="n">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="J30" t="n">
-        <v>4.1</v>
+        <v>2.96</v>
       </c>
       <c r="K30" t="n">
-        <v>5.4</v>
+        <v>100</v>
       </c>
       <c r="L30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="R30" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH30" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BI30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ30" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BK30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL30" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="BM30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN30" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BO30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP30" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BQ30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR30" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BS30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT30" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BU30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV30" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="BW30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX30" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BY30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ30" t="n">
         <v>0</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -8226,16 +8226,16 @@
         <v>3.15</v>
       </c>
       <c r="G31" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="H31" t="n">
         <v>2.12</v>
       </c>
       <c r="I31" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J31" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="K31" t="n">
         <v>4.8</v>
@@ -8247,19 +8247,19 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.1</v>
+        <v>2.46</v>
       </c>
       <c r="O31" t="n">
         <v>1.24</v>
       </c>
       <c r="P31" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S31" t="n">
         <v>2.58</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -8722,226 +8722,226 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury Merogis</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chateauroux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F33" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K33" t="n">
         <v>4.1</v>
       </c>
-      <c r="G33" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="J33" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K33" t="n">
-        <v>4.4</v>
-      </c>
       <c r="L33" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="M33" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N33" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH33" t="n">
         <v>3.55</v>
       </c>
-      <c r="O33" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U33" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V33" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X33" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE33" t="n">
+      <c r="BI33" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>130</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>22</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV33" t="n">
         <v>24</v>
       </c>
-      <c r="AF33" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>95</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>970</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BI33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ33" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL33" t="n">
-        <v>120</v>
-      </c>
-      <c r="BM33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN33" t="n">
-        <v>9</v>
-      </c>
-      <c r="BO33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP33" t="n">
-        <v>40</v>
-      </c>
-      <c r="BQ33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR33" t="n">
-        <v>48</v>
-      </c>
-      <c r="BS33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT33" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BU33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV33" t="n">
-        <v>15</v>
-      </c>
       <c r="BW33" t="n">
         <v>1.01</v>
       </c>
       <c r="BX33" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BY33" t="n">
         <v>1.01</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -8976,121 +8976,121 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Fleury Merogis</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Chateauroux</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.48</v>
+        <v>4.1</v>
       </c>
       <c r="G34" t="n">
-        <v>2.78</v>
+        <v>4.9</v>
       </c>
       <c r="H34" t="n">
-        <v>2.66</v>
+        <v>1.81</v>
       </c>
       <c r="I34" t="n">
-        <v>2.98</v>
+        <v>1.88</v>
       </c>
       <c r="J34" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="K34" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="L34" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="M34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N34" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="O34" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P34" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V34" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="W34" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q34" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.56</v>
-      </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM34" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP34" t="n">
         <v>1.01</v>
@@ -9147,55 +9147,55 @@
         <v>1.01</v>
       </c>
       <c r="BH34" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="BI34" t="n">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="BJ34" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BK34" t="n">
         <v>1.01</v>
       </c>
       <c r="BL34" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BM34" t="n">
         <v>1.01</v>
       </c>
       <c r="BN34" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BO34" t="n">
         <v>1.01</v>
       </c>
       <c r="BP34" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="BQ34" t="n">
         <v>1.01</v>
       </c>
       <c r="BR34" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BS34" t="n">
         <v>1.01</v>
       </c>
       <c r="BT34" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="BU34" t="n">
         <v>1.01</v>
       </c>
       <c r="BV34" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="BW34" t="n">
         <v>1.01</v>
       </c>
       <c r="BX34" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="BY34" t="n">
         <v>1.01</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
         <v>1.92</v>
       </c>
       <c r="G35" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="H35" t="n">
         <v>3.55</v>
@@ -9254,7 +9254,7 @@
         <v>3.5</v>
       </c>
       <c r="K35" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L35" t="n">
         <v>1.28</v>
@@ -9269,7 +9269,7 @@
         <v>1.22</v>
       </c>
       <c r="P35" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q35" t="n">
         <v>1.58</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -9547,31 +9547,31 @@
         <v>1.62</v>
       </c>
       <c r="X36" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA36" t="n">
         <v>70</v>
       </c>
       <c r="AB36" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC36" t="n">
         <v>8</v>
       </c>
       <c r="AD36" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE36" t="n">
         <v>55</v>
       </c>
       <c r="AF36" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG36" t="n">
         <v>14.5</v>
@@ -9610,7 +9610,7 @@
         <v>16</v>
       </c>
       <c r="AS36" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT36" t="n">
         <v>7.4</v>
@@ -9622,7 +9622,7 @@
         <v>11</v>
       </c>
       <c r="AW36" t="n">
-        <v>40</v>
+        <v>5.2</v>
       </c>
       <c r="AX36" t="n">
         <v>12.5</v>
@@ -9634,25 +9634,25 @@
         <v>18</v>
       </c>
       <c r="BA36" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB36" t="n">
-        <v>32</v>
+        <v>5.1</v>
       </c>
       <c r="BC36" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BD36" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE36" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BF36" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="BG36" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH36" t="n">
         <v>3.15</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -10010,10 +10010,10 @@
         <v>3.05</v>
       </c>
       <c r="I38" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J38" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="K38" t="n">
         <v>4.9</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -10763,7 +10763,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G41" t="n">
         <v>1.82</v>
@@ -10796,7 +10796,7 @@
         <v>2.42</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R41" t="n">
         <v>1.57</v>
@@ -10805,13 +10805,13 @@
         <v>2.36</v>
       </c>
       <c r="T41" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U41" t="n">
         <v>2.28</v>
       </c>
       <c r="V41" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W41" t="n">
         <v>2.2</v>
@@ -10823,10 +10823,10 @@
         <v>27</v>
       </c>
       <c r="Z41" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA41" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB41" t="n">
         <v>14</v>
@@ -10838,7 +10838,7 @@
         <v>23</v>
       </c>
       <c r="AE41" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF41" t="n">
         <v>14.5</v>
@@ -10868,7 +10868,7 @@
         <v>7.8</v>
       </c>
       <c r="AO41" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP41" t="n">
         <v>18.5</v>
@@ -10877,10 +10877,10 @@
         <v>18</v>
       </c>
       <c r="AR41" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AS41" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT41" t="n">
         <v>9.4</v>
@@ -10892,7 +10892,7 @@
         <v>15</v>
       </c>
       <c r="AW41" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX41" t="n">
         <v>9.800000000000001</v>
@@ -10904,7 +10904,7 @@
         <v>13.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB41" t="n">
         <v>13.5</v>
@@ -10916,13 +10916,13 @@
         <v>20</v>
       </c>
       <c r="BE41" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF41" t="n">
         <v>5.8</v>
       </c>
       <c r="BG41" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH41" t="n">
         <v>4.6</v>
@@ -10931,7 +10931,7 @@
         <v>3.5</v>
       </c>
       <c r="BJ41" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK41" t="n">
         <v>4.8</v>
@@ -10940,25 +10940,25 @@
         <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN41" t="n">
         <v>4.9</v>
       </c>
       <c r="BO41" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP41" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ41" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BR41" t="n">
         <v>22</v>
       </c>
       <c r="BS41" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT41" t="n">
         <v>9.199999999999999</v>
@@ -10970,7 +10970,7 @@
         <v>38</v>
       </c>
       <c r="BW41" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX41" t="n">
         <v>40</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -11023,7 +11023,7 @@
         <v>5.5</v>
       </c>
       <c r="H42" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="I42" t="n">
         <v>1.8</v>
@@ -11059,10 +11059,10 @@
         <v>2.58</v>
       </c>
       <c r="T42" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U42" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V42" t="n">
         <v>2.24</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -11280,10 +11280,10 @@
         <v>4.3</v>
       </c>
       <c r="I43" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J43" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K43" t="n">
         <v>4.6</v>
@@ -11292,7 +11292,7 @@
         <v>1.01</v>
       </c>
       <c r="M43" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N43" t="n">
         <v>5.6</v>
@@ -11301,7 +11301,7 @@
         <v>1.18</v>
       </c>
       <c r="P43" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q43" t="n">
         <v>1.53</v>
@@ -11310,16 +11310,16 @@
         <v>1.68</v>
       </c>
       <c r="S43" t="n">
-        <v>1.54</v>
+        <v>1.99</v>
       </c>
       <c r="T43" t="n">
-        <v>1.49</v>
+        <v>1.11</v>
       </c>
       <c r="U43" t="n">
-        <v>2.24</v>
+        <v>1.11</v>
       </c>
       <c r="V43" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W43" t="n">
         <v>2.2</v>
@@ -11337,7 +11337,7 @@
         <v>1000</v>
       </c>
       <c r="AB43" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AC43" t="n">
         <v>970</v>
@@ -11349,7 +11349,7 @@
         <v>60</v>
       </c>
       <c r="AF43" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AG43" t="n">
         <v>970</v>
@@ -11361,7 +11361,7 @@
         <v>55</v>
       </c>
       <c r="AJ43" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK43" t="n">
         <v>970</v>
@@ -11379,58 +11379,58 @@
         <v>42</v>
       </c>
       <c r="AP43" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AR43" t="n">
         <v>2.36</v>
       </c>
-      <c r="AQ43" t="n">
+      <c r="AS43" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BD43" t="n">
         <v>2.32</v>
       </c>
-      <c r="AR43" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW43" t="n">
+      <c r="BE43" t="n">
         <v>2.42</v>
       </c>
-      <c r="AX43" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>2.08</v>
-      </c>
       <c r="BF43" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="BG43" t="n">
-        <v>2.02</v>
+        <v>2.36</v>
       </c>
       <c r="BH43" t="n">
         <v>1000</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -11558,13 +11558,13 @@
         <v>1.78</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="R44" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="S44" t="n">
-        <v>2.56</v>
+        <v>3.7</v>
       </c>
       <c r="T44" t="n">
         <v>1.11</v>
@@ -11690,65 +11690,65 @@
         <v>1000</v>
       </c>
       <c r="BI44" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ44" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK44" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL44" t="n">
         <v>1000</v>
       </c>
       <c r="BM44" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN44" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO44" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP44" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ44" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR44" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS44" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT44" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU44" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BV44" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW44" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX44" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY44" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ44" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA44" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -11779,13 +11779,13 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G45" t="n">
         <v>2.36</v>
       </c>
       <c r="H45" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="I45" t="n">
         <v>3.4</v>
@@ -11797,13 +11797,13 @@
         <v>4.9</v>
       </c>
       <c r="L45" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M45" t="n">
         <v>1.02</v>
       </c>
       <c r="N45" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O45" t="n">
         <v>1.17</v>
@@ -11815,22 +11815,22 @@
         <v>1.46</v>
       </c>
       <c r="R45" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="S45" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="T45" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U45" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V45" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W45" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -12051,7 +12051,7 @@
         <v>7</v>
       </c>
       <c r="L46" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="M46" t="n">
         <v>1.02</v>
@@ -12189,7 +12189,7 @@
         <v>4.9</v>
       </c>
       <c r="BF46" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BG46" t="n">
         <v>4.9</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -12550,7 +12550,7 @@
         <v>6.8</v>
       </c>
       <c r="I48" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J48" t="n">
         <v>4.1</v>
@@ -12589,7 +12589,7 @@
         <v>1.84</v>
       </c>
       <c r="V48" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W48" t="n">
         <v>2.58</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -12882,7 +12882,7 @@
         <v>21</v>
       </c>
       <c r="AI49" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ49" t="n">
         <v>24</v>
@@ -12903,7 +12903,7 @@
         <v>75</v>
       </c>
       <c r="AP49" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ49" t="n">
         <v>12.5</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -13163,49 +13163,49 @@
         <v>5.2</v>
       </c>
       <c r="AR50" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS50" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AT50" t="n">
         <v>5.6</v>
       </c>
       <c r="AU50" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AV50" t="n">
         <v>5.2</v>
       </c>
       <c r="AW50" t="n">
-        <v>3.1</v>
+        <v>2.08</v>
       </c>
       <c r="AX50" t="n">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="AY50" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AZ50" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA50" t="n">
-        <v>2.74</v>
+        <v>2.46</v>
       </c>
       <c r="BB50" t="n">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="BC50" t="n">
-        <v>2.72</v>
+        <v>2.14</v>
       </c>
       <c r="BD50" t="n">
-        <v>2.18</v>
+        <v>1.78</v>
       </c>
       <c r="BE50" t="n">
-        <v>5.2</v>
+        <v>2.56</v>
       </c>
       <c r="BF50" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="BG50" t="n">
         <v>13.5</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -13566,7 +13566,7 @@
         <v>3.1</v>
       </c>
       <c r="I52" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="J52" t="n">
         <v>3.1</v>
@@ -13575,7 +13575,7 @@
         <v>3.9</v>
       </c>
       <c r="L52" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="M52" t="n">
         <v>1.08</v>
@@ -13605,7 +13605,7 @@
         <v>1.86</v>
       </c>
       <c r="V52" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W52" t="n">
         <v>1.6</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -13850,7 +13850,7 @@
         <v>1.31</v>
       </c>
       <c r="S53" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="T53" t="n">
         <v>1.68</v>
@@ -13859,10 +13859,10 @@
         <v>1.86</v>
       </c>
       <c r="V53" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="W53" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="X53" t="n">
         <v>16.5</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -14337,7 +14337,7 @@
         <v>3.7</v>
       </c>
       <c r="L55" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M55" t="n">
         <v>1.07</v>
@@ -14364,7 +14364,7 @@
         <v>1.64</v>
       </c>
       <c r="U55" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="V55" t="n">
         <v>1.57</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -14618,7 +14618,7 @@
         <v>1.77</v>
       </c>
       <c r="U56" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V56" t="n">
         <v>1.37</v>
@@ -14651,7 +14651,7 @@
         <v>55</v>
       </c>
       <c r="AF56" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AG56" t="n">
         <v>13.5</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -14830,7 +14830,7 @@
         <v>3</v>
       </c>
       <c r="G57" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H57" t="n">
         <v>2.36</v>
@@ -14878,7 +14878,7 @@
         <v>1.72</v>
       </c>
       <c r="W57" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X57" t="n">
         <v>24</v>
@@ -14890,7 +14890,7 @@
         <v>18.5</v>
       </c>
       <c r="AA57" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AB57" t="n">
         <v>18.5</v>
@@ -14899,7 +14899,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD57" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE57" t="n">
         <v>21</v>
@@ -14908,7 +14908,7 @@
         <v>25</v>
       </c>
       <c r="AG57" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH57" t="n">
         <v>13.5</v>
@@ -14917,7 +14917,7 @@
         <v>27</v>
       </c>
       <c r="AJ57" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK57" t="n">
         <v>27</v>
@@ -14971,7 +14971,7 @@
         <v>25</v>
       </c>
       <c r="BB57" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BC57" t="n">
         <v>26</v>
@@ -15016,7 +15016,7 @@
         <v>25</v>
       </c>
       <c r="BQ57" t="n">
-        <v>14.5</v>
+        <v>3.95</v>
       </c>
       <c r="BR57" t="n">
         <v>32</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -15338,19 +15338,19 @@
         <v>1.02</v>
       </c>
       <c r="G59" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H59" t="n">
         <v>1.02</v>
       </c>
       <c r="I59" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J59" t="n">
         <v>1.02</v>
       </c>
       <c r="K59" t="n">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="L59" t="n">
         <v>1.01</v>
@@ -15377,10 +15377,10 @@
         <v>1.08</v>
       </c>
       <c r="T59" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U59" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V59" t="n">
         <v>1.01</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -15592,19 +15592,19 @@
         <v>1.02</v>
       </c>
       <c r="G60" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H60" t="n">
         <v>1.02</v>
       </c>
       <c r="I60" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J60" t="n">
         <v>1.02</v>
       </c>
       <c r="K60" t="n">
-        <v>410</v>
+        <v>500</v>
       </c>
       <c r="L60" t="n">
         <v>1.01</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -15876,7 +15876,7 @@
         <v>1.24</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R61" t="n">
         <v>1.18</v>
@@ -15885,10 +15885,10 @@
         <v>1.46</v>
       </c>
       <c r="T61" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U61" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V61" t="n">
         <v>1.01</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -16121,7 +16121,7 @@
         <v>1.01</v>
       </c>
       <c r="N62" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O62" t="n">
         <v>1.39</v>
@@ -16130,7 +16130,7 @@
         <v>1.24</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="R62" t="n">
         <v>1.18</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -16351,13 +16351,13 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="G63" t="n">
         <v>3.65</v>
       </c>
       <c r="H63" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="I63" t="n">
         <v>3.15</v>
@@ -16366,7 +16366,7 @@
         <v>3</v>
       </c>
       <c r="K63" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="L63" t="n">
         <v>1.01</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16629,7 @@
         <v>1.01</v>
       </c>
       <c r="N64" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="O64" t="n">
         <v>1.34</v>
@@ -16641,16 +16641,16 @@
         <v>2</v>
       </c>
       <c r="R64" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S64" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="T64" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U64" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V64" t="n">
         <v>1.14</v>
@@ -16707,7 +16707,7 @@
         <v>1000</v>
       </c>
       <c r="AN64" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO64" t="n">
         <v>1000</v>
@@ -16719,52 +16719,52 @@
         <v>15</v>
       </c>
       <c r="AR64" t="n">
-        <v>2.34</v>
+        <v>2.78</v>
       </c>
       <c r="AS64" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AT64" t="n">
-        <v>1.94</v>
+        <v>2.24</v>
       </c>
       <c r="AU64" t="n">
-        <v>2.02</v>
+        <v>2.36</v>
       </c>
       <c r="AV64" t="n">
         <v>19</v>
       </c>
       <c r="AW64" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AX64" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AY64" t="n">
         <v>2.4</v>
       </c>
-      <c r="AX64" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY64" t="n">
-        <v>2.06</v>
-      </c>
       <c r="AZ64" t="n">
-        <v>2.24</v>
+        <v>2.66</v>
       </c>
       <c r="BA64" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="BB64" t="n">
         <v>11</v>
       </c>
       <c r="BC64" t="n">
-        <v>2.18</v>
+        <v>2.58</v>
       </c>
       <c r="BD64" t="n">
-        <v>2.3</v>
+        <v>2.74</v>
       </c>
       <c r="BE64" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="BF64" t="n">
-        <v>2.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG64" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="BH64" t="n">
         <v>1000</v>
@@ -16828,261 +16828,515 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Torque</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Nacional (Uru)</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G65" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H65" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I65" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J65" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K65" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L65" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N65" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S65" t="n">
+        <v>3</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X65" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU65" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV65" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW65" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX65" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY65" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ65" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA65" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB65" t="n">
+        <v>46</v>
+      </c>
+      <c r="BC65" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD65" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE65" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF65" t="n">
+        <v>28</v>
+      </c>
+      <c r="BG65" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BH65" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI65" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BJ65" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK65" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BL65" t="n">
+        <v>130</v>
+      </c>
+      <c r="BM65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN65" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BO65" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BP65" t="n">
+        <v>32</v>
+      </c>
+      <c r="BQ65" t="n">
+        <v>20</v>
+      </c>
+      <c r="BR65" t="n">
+        <v>44</v>
+      </c>
+      <c r="BS65" t="n">
+        <v>28</v>
+      </c>
+      <c r="BT65" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BU65" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV65" t="n">
+        <v>19</v>
+      </c>
+      <c r="BW65" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX65" t="n">
+        <v>34</v>
+      </c>
+      <c r="BY65" t="n">
+        <v>22</v>
+      </c>
+      <c r="BZ65" t="n">
+        <v>29</v>
+      </c>
+      <c r="CA65" t="n">
+        <v>19</v>
+      </c>
+      <c r="CB65" t="inlineStr">
+        <is>
+          <t>2026-05-13 22:15:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>Venezuelan Primera Division</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>Deportivo La Guaira</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Universidad de Venezuela</t>
         </is>
       </c>
-      <c r="F65" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H65" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J65" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N65" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P65" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R65" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S65" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T65" t="n">
+      <c r="F66" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H66" t="n">
+        <v>4</v>
+      </c>
+      <c r="I66" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J66" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K66" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L66" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N66" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P66" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S66" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T66" t="n">
         <v>1.11</v>
       </c>
-      <c r="U65" t="n">
+      <c r="U66" t="n">
         <v>1.11</v>
       </c>
-      <c r="V65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB65" t="inlineStr">
-        <is>
-          <t>2026-05-13 19:57:10</t>
+      <c r="V66" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB66" t="inlineStr">
+        <is>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-15.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H2" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="I2" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="J2" t="n">
         <v>3.85</v>
       </c>
       <c r="K2" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.27</v>
@@ -881,10 +881,10 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="P2" t="n">
         <v>2.24</v>
@@ -893,25 +893,25 @@
         <v>1.58</v>
       </c>
       <c r="R2" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S2" t="n">
-        <v>2.66</v>
+        <v>2.48</v>
       </c>
       <c r="T2" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U2" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V2" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="W2" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y2" t="n">
         <v>12.5</v>
@@ -920,7 +920,7 @@
         <v>13.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AB2" t="n">
         <v>27</v>
@@ -944,7 +944,7 @@
         <v>24</v>
       </c>
       <c r="AI2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ2" t="n">
         <v>170</v>
@@ -953,10 +953,10 @@
         <v>85</v>
       </c>
       <c r="AL2" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN2" t="n">
         <v>90</v>
@@ -965,22 +965,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AP2" t="n">
-        <v>14.5</v>
+        <v>4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AS2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV2" t="n">
         <v>7.6</v>
@@ -989,37 +989,37 @@
         <v>12</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG2" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI2" t="n">
         <v>3.1</v>
@@ -1037,7 +1037,7 @@
         <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BO2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G3" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J3" t="n">
         <v>3.9</v>
@@ -1129,7 +1129,7 @@
         <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M3" t="n">
         <v>1.04</v>
@@ -1141,7 +1141,7 @@
         <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q3" t="n">
         <v>1.66</v>
@@ -1150,7 +1150,7 @@
         <v>1.55</v>
       </c>
       <c r="S3" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="T3" t="n">
         <v>1.59</v>
@@ -1159,10 +1159,10 @@
         <v>2.62</v>
       </c>
       <c r="V3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="X3" t="n">
         <v>20</v>
@@ -1177,10 +1177,10 @@
         <v>46</v>
       </c>
       <c r="AB3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
         <v>13.5</v>
@@ -1207,7 +1207,7 @@
         <v>23</v>
       </c>
       <c r="AL3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM3" t="n">
         <v>65</v>
@@ -1228,7 +1228,7 @@
         <v>20</v>
       </c>
       <c r="AS3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AT3" t="n">
         <v>12.5</v>
@@ -1264,7 +1264,7 @@
         <v>26</v>
       </c>
       <c r="BE3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BF3" t="n">
         <v>12.5</v>
@@ -1276,19 +1276,19 @@
         <v>4.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="BJ3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN3" t="n">
         <v>5.7</v>
@@ -1300,16 +1300,16 @@
         <v>16.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR3" t="n">
         <v>25</v>
       </c>
       <c r="BS3" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU3" t="n">
         <v>5.1</v>
@@ -1318,13 +1318,13 @@
         <v>21</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BX3" t="n">
         <v>28</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1368,16 +1368,16 @@
         <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>190</v>
+        <v>970</v>
       </c>
       <c r="H4" t="n">
         <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>190</v>
+        <v>970</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K4" t="n">
         <v>110</v>
@@ -1389,13 +1389,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="O4" t="n">
         <v>1.17</v>
       </c>
       <c r="P4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q4" t="n">
         <v>1.17</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1619,31 +1619,31 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="G5" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="H5" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J5" t="n">
         <v>4.1</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O5" t="n">
         <v>1.18</v>
@@ -1652,34 +1652,34 @@
         <v>2.66</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S5" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="T5" t="n">
         <v>1.55</v>
       </c>
       <c r="U5" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="V5" t="n">
         <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="X5" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="Y5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z5" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AA5" t="n">
         <v>65</v>
@@ -1688,22 +1688,22 @@
         <v>15</v>
       </c>
       <c r="AC5" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AE5" t="n">
         <v>36</v>
       </c>
       <c r="AF5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG5" t="n">
         <v>11.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI5" t="n">
         <v>42</v>
@@ -1715,7 +1715,7 @@
         <v>22</v>
       </c>
       <c r="AL5" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AM5" t="n">
         <v>65</v>
@@ -1724,22 +1724,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AO5" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.8</v>
+        <v>18.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="AT5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU5" t="n">
         <v>9.199999999999999</v>
@@ -1748,7 +1748,7 @@
         <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="AX5" t="n">
         <v>14</v>
@@ -1760,25 +1760,25 @@
         <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BB5" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="BC5" t="n">
         <v>16</v>
       </c>
       <c r="BD5" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.4</v>
+        <v>28</v>
       </c>
       <c r="BF5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG5" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BH5" t="n">
         <v>5.1</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="G6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H6" t="n">
         <v>1.65</v>
       </c>
       <c r="I6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="J6" t="n">
         <v>3.95</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1903,13 +1903,13 @@
         <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q6" t="n">
         <v>1.84</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
         <v>3.1</v>
@@ -1918,7 +1918,7 @@
         <v>1.84</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V6" t="n">
         <v>2.34</v>
@@ -1942,7 +1942,7 @@
         <v>25</v>
       </c>
       <c r="AC6" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD6" t="n">
         <v>10.5</v>
@@ -2005,7 +2005,7 @@
         <v>14.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AY6" t="n">
         <v>19</v>
@@ -2017,19 +2017,19 @@
         <v>6</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BG6" t="n">
         <v>8.6</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -2160,19 +2160,19 @@
         <v>2.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V7" t="n">
         <v>1.19</v>
@@ -2181,70 +2181,70 @@
         <v>2.34</v>
       </c>
       <c r="X7" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="Y7" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Z7" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AA7" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AC7" t="n">
         <v>11</v>
       </c>
       <c r="AD7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE7" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AF7" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK7" t="n">
         <v>22</v>
       </c>
-      <c r="AI7" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AL7" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AM7" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN7" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AO7" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="AT7" t="n">
         <v>7.6</v>
@@ -2256,7 +2256,7 @@
         <v>18.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="AX7" t="n">
         <v>9</v>
@@ -2268,25 +2268,25 @@
         <v>17.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BC7" t="n">
         <v>15</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="BF7" t="n">
         <v>7.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH7" t="n">
         <v>4.3</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G8" t="n">
         <v>1.45</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1.47</v>
       </c>
       <c r="H8" t="n">
         <v>7.2</v>
       </c>
       <c r="I8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J8" t="n">
         <v>5.4</v>
@@ -2399,7 +2399,7 @@
         <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="M8" t="n">
         <v>1.03</v>
@@ -2411,7 +2411,7 @@
         <v>1.16</v>
       </c>
       <c r="P8" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q8" t="n">
         <v>1.51</v>
@@ -2420,43 +2420,43 @@
         <v>1.74</v>
       </c>
       <c r="S8" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="T8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U8" t="n">
         <v>2.26</v>
       </c>
       <c r="V8" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W8" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="X8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Y8" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AB8" t="n">
         <v>13</v>
       </c>
       <c r="AC8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE8" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF8" t="n">
         <v>11</v>
@@ -2465,7 +2465,7 @@
         <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
@@ -2477,19 +2477,19 @@
         <v>14.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
       </c>
       <c r="AN8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AO8" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AP8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ8" t="n">
         <v>21</v>
@@ -2513,19 +2513,19 @@
         <v>36</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BC8" t="n">
         <v>12</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -2641,46 +2641,46 @@
         <v>1.8</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I9" t="n">
         <v>5.6</v>
       </c>
       <c r="J9" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K9" t="n">
         <v>4.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
         <v>1.3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="R9" t="n">
         <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="U9" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V9" t="n">
         <v>1.22</v>
@@ -2692,19 +2692,19 @@
         <v>16.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AA9" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD9" t="n">
         <v>22</v>
@@ -2713,10 +2713,10 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
         <v>21</v>
@@ -2728,28 +2728,28 @@
         <v>20</v>
       </c>
       <c r="AK9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL9" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AM9" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AP9" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AQ9" t="n">
         <v>15.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AS9" t="n">
         <v>42</v>
@@ -2767,31 +2767,31 @@
         <v>32</v>
       </c>
       <c r="AX9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
         <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD9" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BE9" t="n">
         <v>40</v>
       </c>
       <c r="BF9" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BG9" t="n">
         <v>34</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>3.6</v>
       </c>
       <c r="G11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H11" t="n">
         <v>2.02</v>
@@ -3155,13 +3155,13 @@
         <v>2.24</v>
       </c>
       <c r="J11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
         <v>4.1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
         <v>1.06</v>
@@ -3170,19 +3170,19 @@
         <v>3.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P11" t="n">
         <v>1.96</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R11" t="n">
         <v>1.37</v>
       </c>
       <c r="S11" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T11" t="n">
         <v>1.61</v>
@@ -3191,34 +3191,34 @@
         <v>1.96</v>
       </c>
       <c r="V11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X11" t="n">
         <v>970</v>
       </c>
       <c r="Y11" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Z11" t="n">
         <v>970</v>
       </c>
       <c r="AA11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AB11" t="n">
         <v>970</v>
       </c>
       <c r="AC11" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD11" t="n">
         <v>970</v>
       </c>
       <c r="AE11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF11" t="n">
         <v>34</v>
@@ -3230,16 +3230,16 @@
         <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ11" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AK11" t="n">
         <v>55</v>
       </c>
       <c r="AL11" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -3260,22 +3260,22 @@
         <v>10</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.3</v>
+        <v>11</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV11" t="n">
         <v>8</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AY11" t="n">
         <v>4.3</v>
@@ -3284,28 +3284,28 @@
         <v>4.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BG11" t="n">
         <v>10.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI11" t="n">
         <v>2.82</v>
@@ -3323,7 +3323,7 @@
         <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BO11" t="n">
         <v>5.4</v>
@@ -3344,7 +3344,7 @@
         <v>5.8</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BV11" t="n">
         <v>970</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
         <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
         <v>1.87</v>
@@ -3505,58 +3505,58 @@
         <v>14</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>600</v>
+        <v>970</v>
       </c>
       <c r="H13" t="n">
         <v>1.04</v>
@@ -3663,7 +3663,7 @@
         <v>970</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="K13" t="n">
         <v>950</v>
@@ -3699,7 +3699,7 @@
         <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -3932,19 +3932,19 @@
         <v>1.25</v>
       </c>
       <c r="O14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P14" t="n">
         <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="R14" t="n">
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -4189,10 +4189,10 @@
         <v>1.2</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="R15" t="n">
         <v>1.08</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -4449,10 +4449,10 @@
         <v>1.14</v>
       </c>
       <c r="R16" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="S16" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
         <v>1.04</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J17" t="n">
         <v>1.04</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -4939,13 +4939,13 @@
         <v>5.9</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M18" t="n">
         <v>1.03</v>
       </c>
       <c r="N18" t="n">
-        <v>2.52</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
         <v>1.15</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>3.15</v>
       </c>
       <c r="G20" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H20" t="n">
         <v>2.22</v>
@@ -5468,13 +5468,13 @@
         <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="T20" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="U20" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="V20" t="n">
         <v>1.67</v>
@@ -5486,7 +5486,7 @@
         <v>970</v>
       </c>
       <c r="Y20" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Z20" t="n">
         <v>970</v>
@@ -5516,13 +5516,13 @@
         <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ20" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AK20" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AL20" t="n">
         <v>60</v>
@@ -5531,10 +5531,10 @@
         <v>110</v>
       </c>
       <c r="AN20" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AO20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP20" t="n">
         <v>1.01</v>
@@ -5543,7 +5543,7 @@
         <v>7.8</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AS20" t="n">
         <v>1.01</v>
@@ -5552,10 +5552,10 @@
         <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV20" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW20" t="n">
         <v>1.01</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -5686,13 +5686,13 @@
         <v>2.7</v>
       </c>
       <c r="G21" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="H21" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="I21" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J21" t="n">
         <v>3.5</v>
@@ -5716,7 +5716,7 @@
         <v>2.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="R21" t="n">
         <v>1.42</v>
@@ -5725,19 +5725,19 @@
         <v>3.1</v>
       </c>
       <c r="T21" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="U21" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="V21" t="n">
         <v>1.54</v>
       </c>
       <c r="W21" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X21" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y21" t="n">
         <v>14.5</v>
@@ -5749,7 +5749,7 @@
         <v>46</v>
       </c>
       <c r="AB21" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC21" t="n">
         <v>9.4</v>
@@ -5761,19 +5761,19 @@
         <v>34</v>
       </c>
       <c r="AF21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG21" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH21" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI21" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ21" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AK21" t="n">
         <v>34</v>
@@ -5791,76 +5791,76 @@
         <v>25</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="AQ21" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AR21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC21" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA21" t="n">
+      <c r="BD21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE21" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>5.2</v>
       </c>
       <c r="BF21" t="n">
         <v>17</v>
       </c>
       <c r="BG21" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BH21" t="n">
         <v>4.1</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="BJ21" t="n">
         <v>10.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BL21" t="n">
         <v>120</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BN21" t="n">
         <v>6.8</v>
@@ -5872,13 +5872,13 @@
         <v>24</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BR21" t="n">
         <v>36</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BT21" t="n">
         <v>6.6</v>
@@ -5890,23 +5890,23 @@
         <v>23</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BX21" t="n">
         <v>34</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BZ21" t="n">
         <v>26</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -5946,10 +5946,10 @@
         <v>2.02</v>
       </c>
       <c r="I22" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K22" t="n">
         <v>4.5</v>
@@ -5970,28 +5970,28 @@
         <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="R22" t="n">
         <v>1.56</v>
       </c>
       <c r="S22" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="T22" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="U22" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="V22" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="W22" t="n">
         <v>1.35</v>
       </c>
       <c r="X22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y22" t="n">
         <v>16</v>
@@ -6021,7 +6021,7 @@
         <v>17.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI22" t="n">
         <v>32</v>
@@ -6054,7 +6054,7 @@
         <v>12.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AT22" t="n">
         <v>14</v>
@@ -6063,7 +6063,7 @@
         <v>7.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW22" t="n">
         <v>15</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O23" t="n">
         <v>1.16</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
         <v>4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P24" t="n">
         <v>2.06</v>
@@ -6484,7 +6484,7 @@
         <v>1.41</v>
       </c>
       <c r="S24" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
         <v>1.73</v>
@@ -6499,7 +6499,7 @@
         <v>1.29</v>
       </c>
       <c r="X24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y24" t="n">
         <v>12.5</v>
@@ -6517,16 +6517,16 @@
         <v>10.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE24" t="n">
         <v>25</v>
       </c>
       <c r="AF24" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AG24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH24" t="n">
         <v>21</v>
@@ -6553,55 +6553,55 @@
         <v>15.5</v>
       </c>
       <c r="AP24" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR24" t="n">
         <v>11.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.6</v>
+        <v>12</v>
       </c>
       <c r="AU24" t="n">
         <v>7.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AW24" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AX24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC24" t="n">
         <v>3.95</v>
       </c>
-      <c r="AY24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BA24" t="n">
+      <c r="BD24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF24" t="n">
         <v>3.95</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>4.1</v>
       </c>
       <c r="BG24" t="n">
         <v>9.4</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -6699,13 +6699,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G25" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="H25" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="I25" t="n">
         <v>2.02</v>
@@ -6723,7 +6723,7 @@
         <v>1.04</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O25" t="n">
         <v>1.2</v>
@@ -6732,13 +6732,13 @@
         <v>2.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="R25" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T25" t="n">
         <v>1.11</v>
@@ -6750,7 +6750,7 @@
         <v>1.98</v>
       </c>
       <c r="W25" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="G26" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H26" t="n">
         <v>3.25</v>
@@ -6965,10 +6965,10 @@
         <v>5.2</v>
       </c>
       <c r="J26" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K26" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -6977,34 +6977,34 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="O26" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="P26" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="R26" t="n">
         <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="T26" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V26" t="n">
         <v>1.24</v>
       </c>
       <c r="W26" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -7207,22 +7207,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G27" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I27" t="n">
         <v>7.8</v>
       </c>
       <c r="J27" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K27" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -7234,7 +7234,7 @@
         <v>1.86</v>
       </c>
       <c r="O27" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="P27" t="n">
         <v>1.86</v>
@@ -7249,10 +7249,10 @@
         <v>1.69</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V27" t="n">
         <v>1.14</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
         <v>2.48</v>
       </c>
       <c r="I28" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
         <v>3.75</v>
@@ -7479,7 +7479,7 @@
         <v>4.5</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M28" t="n">
         <v>1.05</v>
@@ -7488,7 +7488,7 @@
         <v>4.4</v>
       </c>
       <c r="O28" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P28" t="n">
         <v>2.18</v>
@@ -7497,7 +7497,7 @@
         <v>1.64</v>
       </c>
       <c r="R28" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S28" t="n">
         <v>2.62</v>
@@ -7509,7 +7509,7 @@
         <v>2.2</v>
       </c>
       <c r="V28" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W28" t="n">
         <v>1.5</v>
@@ -7518,7 +7518,7 @@
         <v>22</v>
       </c>
       <c r="Y28" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="Z28" t="n">
         <v>22</v>
@@ -7527,25 +7527,25 @@
         <v>42</v>
       </c>
       <c r="AB28" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AC28" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD28" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AE28" t="n">
         <v>30</v>
       </c>
       <c r="AF28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG28" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AH28" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AI28" t="n">
         <v>40</v>
@@ -7569,16 +7569,16 @@
         <v>21</v>
       </c>
       <c r="AP28" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28" t="n">
         <v>10</v>
       </c>
       <c r="AR28" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AS28" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AT28" t="n">
         <v>10.5</v>
@@ -7590,91 +7590,91 @@
         <v>9.4</v>
       </c>
       <c r="AW28" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX28" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AY28" t="n">
         <v>10</v>
       </c>
       <c r="AZ28" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA28" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BB28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>110</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>65</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>24</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>22</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>21</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BX28" t="n">
         <v>32</v>
       </c>
-      <c r="BC28" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX28" t="n">
-        <v>1000</v>
-      </c>
       <c r="BY28" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BZ28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -7969,25 +7969,25 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="G30" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="H30" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I30" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="J30" t="n">
         <v>3.5</v>
       </c>
       <c r="K30" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L30" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M30" t="n">
         <v>1.08</v>
@@ -7999,52 +7999,52 @@
         <v>1.38</v>
       </c>
       <c r="P30" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="R30" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T30" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U30" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V30" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W30" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="X30" t="n">
         <v>12</v>
       </c>
       <c r="Y30" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA30" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AB30" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE30" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF30" t="n">
         <v>11</v>
@@ -8053,10 +8053,10 @@
         <v>10.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AI30" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AJ30" t="n">
         <v>22</v>
@@ -8068,67 +8068,67 @@
         <v>44</v>
       </c>
       <c r="AM30" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN30" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AO30" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP30" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
         <v>30</v>
       </c>
       <c r="AS30" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT30" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU30" t="n">
         <v>7.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>8.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX30" t="n">
         <v>9.4</v>
       </c>
       <c r="AY30" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ30" t="n">
-        <v>8.6</v>
+        <v>18.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB30" t="n">
         <v>18</v>
       </c>
       <c r="BC30" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD30" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE30" t="n">
         <v>10.5</v>
       </c>
-      <c r="BE30" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BF30" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG30" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BH30" t="n">
         <v>3.5</v>
@@ -8137,7 +8137,7 @@
         <v>2.62</v>
       </c>
       <c r="BJ30" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK30" t="n">
         <v>1.01</v>
@@ -8152,7 +8152,7 @@
         <v>5</v>
       </c>
       <c r="BO30" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP30" t="n">
         <v>16</v>
@@ -8167,7 +8167,7 @@
         <v>1.01</v>
       </c>
       <c r="BT30" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BU30" t="n">
         <v>1.01</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -8247,13 +8247,13 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O31" t="n">
         <v>1.14</v>
       </c>
       <c r="P31" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q31" t="n">
         <v>1.14</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -8480,16 +8480,16 @@
         <v>2.6</v>
       </c>
       <c r="G32" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="H32" t="n">
         <v>2.48</v>
       </c>
       <c r="I32" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="J32" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K32" t="n">
         <v>4.3</v>
@@ -8516,19 +8516,19 @@
         <v>1.61</v>
       </c>
       <c r="S32" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="T32" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="U32" t="n">
-        <v>2.42</v>
+        <v>2.64</v>
       </c>
       <c r="V32" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W32" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="X32" t="n">
         <v>29</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -8740,13 +8740,13 @@
         <v>1.52</v>
       </c>
       <c r="I33" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="J33" t="n">
         <v>3.5</v>
       </c>
       <c r="K33" t="n">
-        <v>100</v>
+        <v>6.4</v>
       </c>
       <c r="L33" t="n">
         <v>1.31</v>
@@ -8755,16 +8755,16 @@
         <v>1.06</v>
       </c>
       <c r="N33" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="O33" t="n">
         <v>1.29</v>
       </c>
       <c r="P33" t="n">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R33" t="n">
         <v>1.37</v>
@@ -8773,10 +8773,10 @@
         <v>2.86</v>
       </c>
       <c r="T33" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="U33" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="V33" t="n">
         <v>2.44</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -8988,13 +8988,13 @@
         <v>3.65</v>
       </c>
       <c r="G34" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H34" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="I34" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="J34" t="n">
         <v>4.3</v>
@@ -9009,10 +9009,10 @@
         <v>1.02</v>
       </c>
       <c r="N34" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O34" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P34" t="n">
         <v>3</v>
@@ -9033,115 +9033,115 @@
         <v>2.86</v>
       </c>
       <c r="V34" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="W34" t="n">
         <v>1.33</v>
       </c>
       <c r="X34" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="Y34" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Z34" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AA34" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN34" t="n">
         <v>25</v>
       </c>
-      <c r="AB34" t="n">
-        <v>26</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>970</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>29</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>48</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>970</v>
-      </c>
       <c r="AO34" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AP34" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="AQ34" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="AR34" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="AS34" t="n">
-        <v>7.4</v>
+        <v>4</v>
       </c>
       <c r="AT34" t="n">
-        <v>7.4</v>
+        <v>4</v>
       </c>
       <c r="AU34" t="n">
         <v>10</v>
       </c>
       <c r="AV34" t="n">
-        <v>5.6</v>
+        <v>3.45</v>
       </c>
       <c r="AW34" t="n">
-        <v>6.6</v>
+        <v>3.85</v>
       </c>
       <c r="AX34" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="AY34" t="n">
-        <v>12.5</v>
+        <v>3.75</v>
       </c>
       <c r="AZ34" t="n">
         <v>13</v>
       </c>
       <c r="BA34" t="n">
-        <v>7.6</v>
+        <v>4</v>
       </c>
       <c r="BB34" t="n">
-        <v>9.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="BC34" t="n">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BD34" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="BE34" t="n">
-        <v>8.6</v>
+        <v>4.3</v>
       </c>
       <c r="BF34" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="BG34" t="n">
         <v>6.2</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9245,7 @@
         <v>1.59</v>
       </c>
       <c r="H35" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="I35" t="n">
         <v>10</v>
@@ -9281,10 +9281,10 @@
         <v>2.16</v>
       </c>
       <c r="T35" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="U35" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="V35" t="n">
         <v>1.11</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -9493,22 +9493,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="G36" t="n">
         <v>3.25</v>
       </c>
       <c r="H36" t="n">
-        <v>2.52</v>
+        <v>1.09</v>
       </c>
       <c r="I36" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J36" t="n">
-        <v>1.1</v>
+        <v>2.42</v>
       </c>
       <c r="K36" t="n">
-        <v>5.4</v>
+        <v>100</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -10034,7 +10034,7 @@
         <v>1.94</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="R38" t="n">
         <v>1.38</v>
@@ -10043,10 +10043,10 @@
         <v>2.8</v>
       </c>
       <c r="T38" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="U38" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="V38" t="n">
         <v>1.26</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
         <v>2.12</v>
       </c>
       <c r="I39" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="J39" t="n">
         <v>3.45</v>
@@ -10279,7 +10279,7 @@
         <v>1.05</v>
       </c>
       <c r="N39" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O39" t="n">
         <v>1.24</v>
@@ -10288,7 +10288,7 @@
         <v>2.14</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="R39" t="n">
         <v>1.45</v>
@@ -10300,13 +10300,13 @@
         <v>1.57</v>
       </c>
       <c r="U39" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="V39" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W39" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X39" t="n">
         <v>22</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -10533,28 +10533,28 @@
         <v>1.05</v>
       </c>
       <c r="N40" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="O40" t="n">
         <v>1.26</v>
       </c>
       <c r="P40" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="R40" t="n">
         <v>1.43</v>
       </c>
       <c r="S40" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="T40" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="U40" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="V40" t="n">
         <v>1.5</v>
@@ -10671,13 +10671,13 @@
         <v>1.01</v>
       </c>
       <c r="BH40" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BI40" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BJ40" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BK40" t="n">
         <v>1.01</v>
@@ -10689,7 +10689,7 @@
         <v>1.01</v>
       </c>
       <c r="BN40" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BO40" t="n">
         <v>1.01</v>
@@ -10719,7 +10719,7 @@
         <v>1.01</v>
       </c>
       <c r="BX40" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BY40" t="n">
         <v>1.01</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -10793,25 +10793,25 @@
         <v>1.25</v>
       </c>
       <c r="P41" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q41" t="n">
         <v>1.72</v>
       </c>
       <c r="R41" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S41" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="T41" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U41" t="n">
         <v>2.04</v>
       </c>
       <c r="V41" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="W41" t="n">
         <v>1.22</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -11035,10 +11035,10 @@
         <v>4.7</v>
       </c>
       <c r="L42" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M42" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N42" t="n">
         <v>2.32</v>
@@ -11050,10 +11050,10 @@
         <v>2.12</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R42" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S42" t="n">
         <v>2.2</v>
@@ -11071,58 +11071,58 @@
         <v>2.06</v>
       </c>
       <c r="X42" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y42" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z42" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA42" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB42" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC42" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE42" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF42" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH42" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI42" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK42" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL42" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM42" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN42" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO42" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP42" t="n">
         <v>1.01</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11274,7 @@
         <v>1.95</v>
       </c>
       <c r="G43" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="H43" t="n">
         <v>3.55</v>
@@ -11289,40 +11289,40 @@
         <v>4.4</v>
       </c>
       <c r="L43" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M43" t="n">
         <v>1.04</v>
       </c>
       <c r="N43" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="O43" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P43" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q43" t="n">
         <v>1.58</v>
       </c>
       <c r="R43" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S43" t="n">
         <v>2.44</v>
       </c>
       <c r="T43" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U43" t="n">
         <v>2.2</v>
       </c>
       <c r="V43" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W43" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="X43" t="n">
         <v>1000</v>
@@ -11433,10 +11433,10 @@
         <v>1.01</v>
       </c>
       <c r="BH43" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI43" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BJ43" t="n">
         <v>10.5</v>
@@ -11445,7 +11445,7 @@
         <v>1.01</v>
       </c>
       <c r="BL43" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BM43" t="n">
         <v>1.01</v>
@@ -11454,7 +11454,7 @@
         <v>5.8</v>
       </c>
       <c r="BO43" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP43" t="n">
         <v>15.5</v>
@@ -11472,7 +11472,7 @@
         <v>8.4</v>
       </c>
       <c r="BU43" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV43" t="n">
         <v>32</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -11549,79 +11549,79 @@
         <v>1.11</v>
       </c>
       <c r="N44" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="O44" t="n">
         <v>1.48</v>
       </c>
       <c r="P44" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="R44" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S44" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="T44" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U44" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V44" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W44" t="n">
         <v>1.62</v>
       </c>
       <c r="X44" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y44" t="n">
         <v>10.5</v>
       </c>
       <c r="Z44" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA44" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB44" t="n">
         <v>8.6</v>
       </c>
       <c r="AC44" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD44" t="n">
         <v>15.5</v>
       </c>
       <c r="AE44" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AF44" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AG44" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH44" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI44" t="n">
         <v>70</v>
       </c>
       <c r="AJ44" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AK44" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL44" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM44" t="n">
         <v>170</v>
@@ -11630,61 +11630,61 @@
         <v>36</v>
       </c>
       <c r="AO44" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AP44" t="n">
         <v>8.6</v>
       </c>
       <c r="AQ44" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR44" t="n">
         <v>19</v>
       </c>
       <c r="AS44" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT44" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU44" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV44" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="AW44" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AX44" t="n">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="AY44" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ44" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC44" t="n">
         <v>7.4</v>
       </c>
-      <c r="BA44" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BD44" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BE44" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF44" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG44" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH44" t="n">
         <v>3.2</v>
@@ -11726,16 +11726,16 @@
         <v>7.2</v>
       </c>
       <c r="BU44" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV44" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW44" t="n">
         <v>1.01</v>
       </c>
       <c r="BX44" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY44" t="n">
         <v>1.01</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="G45" t="n">
         <v>1.83</v>
@@ -11800,7 +11800,7 @@
         <v>1.01</v>
       </c>
       <c r="M45" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N45" t="n">
         <v>4.1</v>
@@ -11812,19 +11812,19 @@
         <v>2.1</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="R45" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T45" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="U45" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="V45" t="n">
         <v>1.22</v>
@@ -11833,28 +11833,28 @@
         <v>2.2</v>
       </c>
       <c r="X45" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Y45" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z45" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AA45" t="n">
         <v>140</v>
       </c>
       <c r="AB45" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC45" t="n">
         <v>11</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>9.4</v>
       </c>
       <c r="AD45" t="n">
         <v>23</v>
       </c>
       <c r="AE45" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF45" t="n">
         <v>13</v>
@@ -11863,19 +11863,19 @@
         <v>12</v>
       </c>
       <c r="AH45" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AI45" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ45" t="n">
         <v>22</v>
       </c>
       <c r="AK45" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL45" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -11884,61 +11884,61 @@
         <v>11.5</v>
       </c>
       <c r="AO45" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AP45" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV45" t="n">
         <v>15</v>
       </c>
-      <c r="AQ45" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AW45" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="AX45" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY45" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ45" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA45" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="BB45" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BC45" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD45" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="BE45" t="n">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="BF45" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG45" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="BH45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -12033,10 +12033,10 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="G46" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H46" t="n">
         <v>3.15</v>
@@ -12045,7 +12045,7 @@
         <v>3.65</v>
       </c>
       <c r="J46" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="K46" t="n">
         <v>4.9</v>
@@ -12057,10 +12057,10 @@
         <v>1.01</v>
       </c>
       <c r="N46" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="O46" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="P46" t="n">
         <v>2.84</v>
@@ -12081,10 +12081,10 @@
         <v>2.74</v>
       </c>
       <c r="V46" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W46" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="X46" t="n">
         <v>40</v>
@@ -12123,19 +12123,19 @@
         <v>38</v>
       </c>
       <c r="AJ46" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK46" t="n">
         <v>23</v>
       </c>
       <c r="AL46" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM46" t="n">
         <v>60</v>
       </c>
       <c r="AN46" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AO46" t="n">
         <v>21</v>
@@ -12153,7 +12153,7 @@
         <v>1.01</v>
       </c>
       <c r="AT46" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU46" t="n">
         <v>8.4</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -12293,10 +12293,10 @@
         <v>1.64</v>
       </c>
       <c r="H47" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I47" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J47" t="n">
         <v>4.6</v>
@@ -12308,16 +12308,16 @@
         <v>1.22</v>
       </c>
       <c r="M47" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N47" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O47" t="n">
         <v>1.15</v>
       </c>
       <c r="P47" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="Q47" t="n">
         <v>1.4</v>
@@ -12497,7 +12497,7 @@
         <v>1.01</v>
       </c>
       <c r="BX47" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY47" t="n">
         <v>1.01</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
         <v>9.6</v>
       </c>
       <c r="AU48" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV48" t="n">
         <v>11.5</v>
@@ -12724,7 +12724,7 @@
         <v>5.4</v>
       </c>
       <c r="BO48" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="BP48" t="n">
         <v>1000</v>
@@ -12742,7 +12742,7 @@
         <v>7.8</v>
       </c>
       <c r="BU48" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV48" t="n">
         <v>1000</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -12801,7 +12801,7 @@
         <v>5.3</v>
       </c>
       <c r="H49" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="I49" t="n">
         <v>1.85</v>
@@ -12810,7 +12810,7 @@
         <v>3.95</v>
       </c>
       <c r="K49" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L49" t="n">
         <v>1.26</v>
@@ -12819,22 +12819,22 @@
         <v>1.04</v>
       </c>
       <c r="N49" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O49" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P49" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q49" t="n">
         <v>1.65</v>
       </c>
       <c r="R49" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S49" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="T49" t="n">
         <v>1.67</v>
@@ -12852,28 +12852,28 @@
         <v>26</v>
       </c>
       <c r="Y49" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA49" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB49" t="n">
         <v>25</v>
       </c>
       <c r="AC49" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AD49" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE49" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF49" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AG49" t="n">
         <v>23</v>
@@ -12882,7 +12882,7 @@
         <v>22</v>
       </c>
       <c r="AI49" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ49" t="n">
         <v>130</v>
@@ -12903,13 +12903,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AP49" t="n">
-        <v>4.4</v>
+        <v>15</v>
       </c>
       <c r="AQ49" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR49" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AS49" t="n">
         <v>13.5</v>
@@ -12918,43 +12918,43 @@
         <v>15</v>
       </c>
       <c r="AU49" t="n">
-        <v>3.55</v>
+        <v>7.2</v>
       </c>
       <c r="AV49" t="n">
         <v>7.6</v>
       </c>
       <c r="AW49" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX49" t="n">
         <v>4.2</v>
       </c>
-      <c r="AX49" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AY49" t="n">
-        <v>4.3</v>
+        <v>13.5</v>
       </c>
       <c r="AZ49" t="n">
-        <v>4.3</v>
+        <v>12.5</v>
       </c>
       <c r="BA49" t="n">
         <v>21</v>
       </c>
       <c r="BB49" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BC49" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BD49" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BE49" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BF49" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BG49" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH49" t="n">
         <v>4.2</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -13049,7 +13049,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="G50" t="n">
         <v>1.82</v>
@@ -13058,7 +13058,7 @@
         <v>4.6</v>
       </c>
       <c r="I50" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J50" t="n">
         <v>4.1</v>
@@ -13091,7 +13091,7 @@
         <v>2.36</v>
       </c>
       <c r="T50" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U50" t="n">
         <v>2.28</v>
@@ -13100,19 +13100,19 @@
         <v>1.21</v>
       </c>
       <c r="W50" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X50" t="n">
         <v>29</v>
       </c>
       <c r="Y50" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z50" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA50" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB50" t="n">
         <v>14</v>
@@ -13124,19 +13124,19 @@
         <v>23</v>
       </c>
       <c r="AE50" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF50" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG50" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH50" t="n">
         <v>20</v>
       </c>
       <c r="AI50" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ50" t="n">
         <v>21</v>
@@ -13148,13 +13148,13 @@
         <v>32</v>
       </c>
       <c r="AM50" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AN50" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AO50" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP50" t="n">
         <v>18.5</v>
@@ -13163,10 +13163,10 @@
         <v>18</v>
       </c>
       <c r="AR50" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="AS50" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="AT50" t="n">
         <v>9.4</v>
@@ -13178,7 +13178,7 @@
         <v>15</v>
       </c>
       <c r="AW50" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="AX50" t="n">
         <v>9.800000000000001</v>
@@ -13190,25 +13190,25 @@
         <v>13</v>
       </c>
       <c r="BA50" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BB50" t="n">
         <v>14</v>
       </c>
       <c r="BC50" t="n">
-        <v>4.4</v>
+        <v>12</v>
       </c>
       <c r="BD50" t="n">
         <v>20</v>
       </c>
       <c r="BE50" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BF50" t="n">
         <v>5.8</v>
       </c>
       <c r="BG50" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BH50" t="n">
         <v>4.6</v>
@@ -13232,7 +13232,7 @@
         <v>4.9</v>
       </c>
       <c r="BO50" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BP50" t="n">
         <v>11.5</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -13384,7 +13384,7 @@
         <v>1000</v>
       </c>
       <c r="AG51" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH51" t="n">
         <v>1000</v>
@@ -13411,58 +13411,58 @@
         <v>1000</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AT51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AU51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AV51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AW51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BA51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BD51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BG51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BH51" t="n">
         <v>1000</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -13566,43 +13566,43 @@
         <v>2.94</v>
       </c>
       <c r="I52" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="J52" t="n">
         <v>3.2</v>
       </c>
       <c r="K52" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L52" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M52" t="n">
         <v>1.08</v>
       </c>
       <c r="N52" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O52" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P52" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="R52" t="n">
         <v>1.3</v>
       </c>
       <c r="S52" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T52" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="U52" t="n">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="V52" t="n">
         <v>1.44</v>
@@ -13611,19 +13611,19 @@
         <v>1.57</v>
       </c>
       <c r="X52" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y52" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y52" t="n">
+      <c r="Z52" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB52" t="n">
         <v>12</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>10.5</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
@@ -13632,37 +13632,37 @@
         <v>14.5</v>
       </c>
       <c r="AE52" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AF52" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AG52" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AH52" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AI52" t="n">
         <v>55</v>
       </c>
       <c r="AJ52" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AK52" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AL52" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM52" t="n">
         <v>130</v>
       </c>
       <c r="AN52" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AO52" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AP52" t="n">
         <v>10.5</v>
@@ -13671,22 +13671,22 @@
         <v>9.6</v>
       </c>
       <c r="AR52" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU52" t="n">
         <v>6.4</v>
       </c>
-      <c r="AS52" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AV52" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AW52" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="AX52" t="n">
         <v>14</v>
@@ -13695,34 +13695,34 @@
         <v>10</v>
       </c>
       <c r="AZ52" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="BA52" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="BB52" t="n">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="BC52" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="BD52" t="n">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="BE52" t="n">
-        <v>8.4</v>
+        <v>5.3</v>
       </c>
       <c r="BF52" t="n">
-        <v>19</v>
+        <v>4.6</v>
       </c>
       <c r="BG52" t="n">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="BH52" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BI52" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BJ52" t="n">
         <v>12</v>
@@ -13743,22 +13743,22 @@
         <v>4.1</v>
       </c>
       <c r="BP52" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BQ52" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BR52" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BS52" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BT52" t="n">
         <v>7.4</v>
       </c>
       <c r="BU52" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="BV52" t="n">
         <v>32</v>
@@ -13773,14 +13773,14 @@
         <v>4.4</v>
       </c>
       <c r="BZ52" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="CA52" t="n">
         <v>4.3</v>
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -13814,13 +13814,13 @@
         <v>2.12</v>
       </c>
       <c r="G53" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="H53" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="I53" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J53" t="n">
         <v>3.6</v>
@@ -13835,7 +13835,7 @@
         <v>1.03</v>
       </c>
       <c r="N53" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O53" t="n">
         <v>1.17</v>
@@ -13847,10 +13847,10 @@
         <v>1.48</v>
       </c>
       <c r="R53" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S53" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="T53" t="n">
         <v>1.11</v>
@@ -13862,7 +13862,7 @@
         <v>1.42</v>
       </c>
       <c r="W53" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="X53" t="n">
         <v>1000</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -14071,7 +14071,7 @@
         <v>1.35</v>
       </c>
       <c r="H54" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I54" t="n">
         <v>12</v>
@@ -14080,7 +14080,7 @@
         <v>6.2</v>
       </c>
       <c r="K54" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L54" t="n">
         <v>1.01</v>
@@ -14095,16 +14095,16 @@
         <v>1.15</v>
       </c>
       <c r="P54" t="n">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="R54" t="n">
         <v>1.78</v>
       </c>
       <c r="S54" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="T54" t="n">
         <v>1.85</v>
@@ -14116,31 +14116,31 @@
         <v>1.09</v>
       </c>
       <c r="W54" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="X54" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="Y54" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="Z54" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AA54" t="n">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="AB54" t="n">
         <v>13</v>
       </c>
       <c r="AC54" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AD54" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AE54" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AF54" t="n">
         <v>10.5</v>
@@ -14149,40 +14149,40 @@
         <v>11.5</v>
       </c>
       <c r="AH54" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AI54" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ54" t="n">
         <v>11.5</v>
       </c>
       <c r="AK54" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL54" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM54" t="n">
         <v>130</v>
       </c>
       <c r="AN54" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AO54" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AP54" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AQ54" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AR54" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AS54" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="AT54" t="n">
         <v>11</v>
@@ -14191,10 +14191,10 @@
         <v>13</v>
       </c>
       <c r="AV54" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AW54" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX54" t="n">
         <v>9</v>
@@ -14203,10 +14203,10 @@
         <v>10</v>
       </c>
       <c r="AZ54" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BA54" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BB54" t="n">
         <v>10</v>
@@ -14215,16 +14215,16 @@
         <v>12</v>
       </c>
       <c r="BD54" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BE54" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="BF54" t="n">
         <v>3.6</v>
       </c>
       <c r="BG54" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH54" t="n">
         <v>1000</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -14340,13 +14340,13 @@
         <v>1.01</v>
       </c>
       <c r="M55" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N55" t="n">
-        <v>2.4</v>
+        <v>3.65</v>
       </c>
       <c r="O55" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="P55" t="n">
         <v>1.9</v>
@@ -14361,10 +14361,10 @@
         <v>3.25</v>
       </c>
       <c r="T55" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U55" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="V55" t="n">
         <v>1.13</v>
@@ -14412,7 +14412,7 @@
         <v>18.5</v>
       </c>
       <c r="AK55" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL55" t="n">
         <v>1000</v>
@@ -14427,40 +14427,40 @@
         <v>1000</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AS55" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AT55" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AU55" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AV55" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AW55" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AX55" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AY55" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="BA55" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="BB55" t="n">
         <v>10</v>
@@ -14469,16 +14469,16 @@
         <v>1.39</v>
       </c>
       <c r="BD55" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="BG55" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="BH55" t="n">
         <v>1000</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -14591,7 +14591,7 @@
         <v>3.8</v>
       </c>
       <c r="L56" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M56" t="n">
         <v>1.08</v>
@@ -14735,13 +14735,13 @@
         <v>7.4</v>
       </c>
       <c r="BH56" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI56" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BJ56" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK56" t="n">
         <v>1.01</v>
@@ -14753,13 +14753,13 @@
         <v>1.01</v>
       </c>
       <c r="BN56" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BO56" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP56" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BQ56" t="n">
         <v>1.01</v>
@@ -14771,32 +14771,32 @@
         <v>1.01</v>
       </c>
       <c r="BT56" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BU56" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BV56" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BW56" t="n">
         <v>1.01</v>
       </c>
       <c r="BX56" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BY56" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ56" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="CA56" t="n">
         <v>1.01</v>
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -14836,7 +14836,7 @@
         <v>1.73</v>
       </c>
       <c r="I57" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="J57" t="n">
         <v>3.8</v>
@@ -14857,7 +14857,7 @@
         <v>1.28</v>
       </c>
       <c r="P57" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q57" t="n">
         <v>1.84</v>
@@ -14869,13 +14869,13 @@
         <v>2.36</v>
       </c>
       <c r="T57" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="U57" t="n">
-        <v>1.11</v>
+        <v>1.88</v>
       </c>
       <c r="V57" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="W57" t="n">
         <v>1.19</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -15084,7 +15084,7 @@
         <v>1.95</v>
       </c>
       <c r="G58" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H58" t="n">
         <v>4.1</v>
@@ -15096,25 +15096,25 @@
         <v>3.45</v>
       </c>
       <c r="K58" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L58" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M58" t="n">
         <v>1.08</v>
       </c>
       <c r="N58" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O58" t="n">
         <v>1.34</v>
       </c>
       <c r="P58" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R58" t="n">
         <v>1.31</v>
@@ -15132,7 +15132,7 @@
         <v>1.27</v>
       </c>
       <c r="W58" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X58" t="n">
         <v>15.5</v>
@@ -15168,7 +15168,7 @@
         <v>23</v>
       </c>
       <c r="AI58" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ58" t="n">
         <v>25</v>
@@ -15189,16 +15189,16 @@
         <v>70</v>
       </c>
       <c r="AP58" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ58" t="n">
         <v>11</v>
       </c>
       <c r="AR58" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS58" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AT58" t="n">
         <v>7.2</v>
@@ -15216,13 +15216,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AY58" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ58" t="n">
         <v>15</v>
       </c>
       <c r="BA58" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB58" t="n">
         <v>17.5</v>
@@ -15231,16 +15231,16 @@
         <v>16.5</v>
       </c>
       <c r="BD58" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE58" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF58" t="n">
         <v>11.5</v>
       </c>
       <c r="BG58" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH58" t="n">
         <v>3.65</v>
@@ -15249,16 +15249,16 @@
         <v>2.92</v>
       </c>
       <c r="BJ58" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK58" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BL58" t="n">
         <v>160</v>
       </c>
       <c r="BM58" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BN58" t="n">
         <v>5.2</v>
@@ -15267,19 +15267,19 @@
         <v>3.7</v>
       </c>
       <c r="BP58" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BQ58" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BR58" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS58" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BT58" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU58" t="n">
         <v>6</v>
@@ -15288,23 +15288,23 @@
         <v>46</v>
       </c>
       <c r="BW58" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BX58" t="n">
         <v>60</v>
       </c>
       <c r="BY58" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BZ58" t="n">
         <v>32</v>
       </c>
       <c r="CA58" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -15347,43 +15347,43 @@
         <v>3.75</v>
       </c>
       <c r="J59" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="K59" t="n">
         <v>3.65</v>
       </c>
       <c r="L59" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="M59" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N59" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O59" t="n">
         <v>1.38</v>
       </c>
       <c r="P59" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R59" t="n">
         <v>1.28</v>
       </c>
       <c r="S59" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T59" t="n">
         <v>1.83</v>
       </c>
       <c r="U59" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V59" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W59" t="n">
         <v>1.64</v>
@@ -15485,22 +15485,22 @@
         <v>1.01</v>
       </c>
       <c r="BD59" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE59" t="n">
         <v>1.01</v>
       </c>
       <c r="BF59" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BG59" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BH59" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI59" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BJ59" t="n">
         <v>11.5</v>
@@ -15509,7 +15509,7 @@
         <v>1.01</v>
       </c>
       <c r="BL59" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="BM59" t="n">
         <v>1.01</v>
@@ -15527,7 +15527,7 @@
         <v>1.01</v>
       </c>
       <c r="BR59" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS59" t="n">
         <v>1.01</v>
@@ -15536,7 +15536,7 @@
         <v>7.4</v>
       </c>
       <c r="BU59" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV59" t="n">
         <v>34</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -15592,19 +15592,19 @@
         <v>2.78</v>
       </c>
       <c r="G60" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H60" t="n">
         <v>2.14</v>
       </c>
       <c r="I60" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="J60" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="K60" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L60" t="n">
         <v>1.35</v>
@@ -15619,7 +15619,7 @@
         <v>1.35</v>
       </c>
       <c r="P60" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Q60" t="n">
         <v>2</v>
@@ -15637,10 +15637,10 @@
         <v>1.11</v>
       </c>
       <c r="V60" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W60" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X60" t="n">
         <v>1000</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -15846,13 +15846,13 @@
         <v>2.28</v>
       </c>
       <c r="G61" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H61" t="n">
         <v>3.25</v>
       </c>
       <c r="I61" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J61" t="n">
         <v>2.88</v>
@@ -15882,19 +15882,19 @@
         <v>1.26</v>
       </c>
       <c r="S61" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="T61" t="n">
         <v>1.86</v>
       </c>
       <c r="U61" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="V61" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W61" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X61" t="n">
         <v>13</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -16115,7 +16115,7 @@
         <v>3.75</v>
       </c>
       <c r="L62" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M62" t="n">
         <v>1.07</v>
@@ -16127,22 +16127,22 @@
         <v>1.3</v>
       </c>
       <c r="P62" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="R62" t="n">
         <v>1.39</v>
       </c>
       <c r="S62" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T62" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U62" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V62" t="n">
         <v>1.56</v>
@@ -16259,10 +16259,10 @@
         <v>6.8</v>
       </c>
       <c r="BH62" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BI62" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="BJ62" t="n">
         <v>10.5</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -16354,7 +16354,7 @@
         <v>1.93</v>
       </c>
       <c r="G63" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="H63" t="n">
         <v>3.95</v>
@@ -16363,13 +16363,13 @@
         <v>5.1</v>
       </c>
       <c r="J63" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K63" t="n">
         <v>4.4</v>
       </c>
       <c r="L63" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="M63" t="n">
         <v>1.07</v>
@@ -16390,7 +16390,7 @@
         <v>1.31</v>
       </c>
       <c r="S63" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="T63" t="n">
         <v>1.69</v>
@@ -16399,10 +16399,10 @@
         <v>1.85</v>
       </c>
       <c r="V63" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="W63" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="X63" t="n">
         <v>16.5</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -16608,13 +16608,13 @@
         <v>3.05</v>
       </c>
       <c r="G64" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H64" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I64" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="J64" t="n">
         <v>3.95</v>
@@ -16638,10 +16638,10 @@
         <v>2.62</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R64" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="S64" t="n">
         <v>2.46</v>
@@ -16650,13 +16650,13 @@
         <v>1.53</v>
       </c>
       <c r="U64" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V64" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W64" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X64" t="n">
         <v>24</v>
@@ -16677,7 +16677,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD64" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE64" t="n">
         <v>21</v>
@@ -16710,7 +16710,7 @@
         <v>18</v>
       </c>
       <c r="AO64" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AP64" t="n">
         <v>22</v>
@@ -16728,19 +16728,19 @@
         <v>18</v>
       </c>
       <c r="AU64" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV64" t="n">
         <v>10.5</v>
       </c>
       <c r="AW64" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AX64" t="n">
         <v>23</v>
       </c>
       <c r="AY64" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ64" t="n">
         <v>12.5</v>
@@ -16755,10 +16755,10 @@
         <v>26</v>
       </c>
       <c r="BD64" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE64" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BF64" t="n">
         <v>17</v>
@@ -16770,13 +16770,13 @@
         <v>5.2</v>
       </c>
       <c r="BI64" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="BJ64" t="n">
         <v>10.5</v>
       </c>
       <c r="BK64" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BL64" t="n">
         <v>90</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -16862,7 +16862,7 @@
         <v>3.05</v>
       </c>
       <c r="G65" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H65" t="n">
         <v>2.32</v>
@@ -16874,10 +16874,10 @@
         <v>3.5</v>
       </c>
       <c r="K65" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L65" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="M65" t="n">
         <v>1.06</v>
@@ -16889,7 +16889,7 @@
         <v>1.28</v>
       </c>
       <c r="P65" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q65" t="n">
         <v>1.75</v>
@@ -16898,10 +16898,10 @@
         <v>1.4</v>
       </c>
       <c r="S65" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T65" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U65" t="n">
         <v>2.26</v>
@@ -16916,115 +16916,115 @@
         <v>19.5</v>
       </c>
       <c r="Y65" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Z65" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AA65" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AB65" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AC65" t="n">
         <v>10.5</v>
       </c>
       <c r="AD65" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AE65" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AF65" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AG65" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AH65" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AI65" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ65" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL65" t="n">
         <v>55</v>
       </c>
-      <c r="AK65" t="n">
+      <c r="AM65" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN65" t="n">
         <v>36</v>
       </c>
-      <c r="AL65" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM65" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN65" t="n">
-        <v>32</v>
-      </c>
       <c r="AO65" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP65" t="n">
-        <v>5.8</v>
+        <v>12</v>
       </c>
       <c r="AQ65" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="AR65" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="AS65" t="n">
-        <v>2.58</v>
+        <v>3.95</v>
       </c>
       <c r="AT65" t="n">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="AU65" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AV65" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="AW65" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="AX65" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AY65" t="n">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="AZ65" t="n">
-        <v>5.8</v>
+        <v>12</v>
       </c>
       <c r="BA65" t="n">
-        <v>2.6</v>
+        <v>25</v>
       </c>
       <c r="BB65" t="n">
-        <v>2.66</v>
+        <v>4.1</v>
       </c>
       <c r="BC65" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="BD65" t="n">
-        <v>2.64</v>
+        <v>4</v>
       </c>
       <c r="BE65" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BF65" t="n">
-        <v>3.15</v>
+        <v>20</v>
       </c>
       <c r="BG65" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH65" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI65" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="BJ65" t="n">
         <v>11</v>
@@ -17057,7 +17057,7 @@
         <v>1.01</v>
       </c>
       <c r="BT65" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU65" t="n">
         <v>4.2</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -17113,19 +17113,19 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G66" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H66" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I66" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J66" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K66" t="n">
         <v>4.6</v>
@@ -17137,31 +17137,31 @@
         <v>1.04</v>
       </c>
       <c r="N66" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O66" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P66" t="n">
         <v>2.46</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R66" t="n">
         <v>1.59</v>
       </c>
       <c r="S66" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T66" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U66" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V66" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W66" t="n">
         <v>2.4</v>
@@ -17179,7 +17179,7 @@
         <v>150</v>
       </c>
       <c r="AB66" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC66" t="n">
         <v>10.5</v>
@@ -17188,7 +17188,7 @@
         <v>22</v>
       </c>
       <c r="AE66" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF66" t="n">
         <v>12.5</v>
@@ -17224,13 +17224,13 @@
         <v>7.6</v>
       </c>
       <c r="AQ66" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR66" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS66" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT66" t="n">
         <v>10</v>
@@ -17242,7 +17242,7 @@
         <v>7.4</v>
       </c>
       <c r="AW66" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX66" t="n">
         <v>10.5</v>
@@ -17254,7 +17254,7 @@
         <v>15.5</v>
       </c>
       <c r="BA66" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB66" t="n">
         <v>15</v>
@@ -17263,16 +17263,16 @@
         <v>14</v>
       </c>
       <c r="BD66" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE66" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF66" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG66" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH66" t="n">
         <v>5</v>
@@ -17299,7 +17299,7 @@
         <v>3.55</v>
       </c>
       <c r="BP66" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ66" t="n">
         <v>1.01</v>
@@ -17317,7 +17317,7 @@
         <v>1.01</v>
       </c>
       <c r="BV66" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BW66" t="n">
         <v>1.01</v>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -17379,7 +17379,7 @@
         <v>990</v>
       </c>
       <c r="J67" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="K67" t="n">
         <v>500</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -17633,7 +17633,7 @@
         <v>990</v>
       </c>
       <c r="J68" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="K68" t="n">
         <v>500</v>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -17875,19 +17875,19 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G69" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="H69" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="I69" t="n">
-        <v>970</v>
+        <v>3.05</v>
       </c>
       <c r="J69" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="K69" t="n">
         <v>6.8</v>
@@ -17908,13 +17908,13 @@
         <v>1.73</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="R69" t="n">
         <v>1.18</v>
       </c>
       <c r="S69" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="T69" t="n">
         <v>1.01</v>
@@ -17923,10 +17923,10 @@
         <v>1.01</v>
       </c>
       <c r="V69" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W69" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="X69" t="n">
         <v>1000</v>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -18162,13 +18162,13 @@
         <v>1.24</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="R70" t="n">
         <v>1.18</v>
       </c>
       <c r="S70" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T70" t="n">
         <v>1.11</v>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -18410,19 +18410,19 @@
         <v>1.24</v>
       </c>
       <c r="O71" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="P71" t="n">
         <v>1.24</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="R71" t="n">
         <v>1.18</v>
       </c>
       <c r="S71" t="n">
-        <v>1.38</v>
+        <v>1.05</v>
       </c>
       <c r="T71" t="n">
         <v>1.11</v>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -18637,166 +18637,166 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="G72" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="H72" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="I72" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="J72" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="K72" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L72" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M72" t="n">
         <v>1.05</v>
       </c>
       <c r="N72" t="n">
-        <v>1.1</v>
+        <v>2.44</v>
       </c>
       <c r="O72" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="P72" t="n">
         <v>1.71</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="R72" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S72" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="T72" t="n">
-        <v>1.11</v>
+        <v>1.99</v>
       </c>
       <c r="U72" t="n">
         <v>1.11</v>
       </c>
       <c r="V72" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="W72" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="X72" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="Y72" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z72" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA72" t="n">
         <v>1000</v>
       </c>
       <c r="AB72" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC72" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD72" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AE72" t="n">
         <v>1000</v>
       </c>
       <c r="AF72" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG72" t="n">
         <v>13.5</v>
       </c>
       <c r="AH72" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI72" t="n">
         <v>1000</v>
       </c>
       <c r="AJ72" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AK72" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AL72" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM72" t="n">
         <v>1000</v>
       </c>
       <c r="AN72" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AO72" t="n">
         <v>1000</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.97</v>
+        <v>2.24</v>
       </c>
       <c r="AQ72" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AR72" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AS72" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="AT72" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AU72" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AV72" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AY72" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AZ72" t="n">
         <v>19</v>
       </c>
-      <c r="AW72" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AX72" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AY72" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AZ72" t="n">
-        <v>2.06</v>
-      </c>
       <c r="BA72" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="BB72" t="n">
-        <v>1.99</v>
+        <v>2.36</v>
       </c>
       <c r="BC72" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="BD72" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="BE72" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="BF72" t="n">
-        <v>7.8</v>
+        <v>2.6</v>
       </c>
       <c r="BG72" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="BH72" t="n">
         <v>1000</v>
@@ -18860,7 +18860,7 @@
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -18894,16 +18894,16 @@
         <v>3.25</v>
       </c>
       <c r="G73" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="H73" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="I73" t="n">
         <v>2.4</v>
       </c>
       <c r="J73" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K73" t="n">
         <v>3.95</v>
@@ -18933,22 +18933,22 @@
         <v>3.15</v>
       </c>
       <c r="T73" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U73" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V73" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W73" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X73" t="n">
         <v>18</v>
       </c>
       <c r="Y73" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z73" t="n">
         <v>17.5</v>
@@ -18969,13 +18969,13 @@
         <v>28</v>
       </c>
       <c r="AF73" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG73" t="n">
         <v>17</v>
       </c>
       <c r="AH73" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI73" t="n">
         <v>42</v>
@@ -18984,7 +18984,7 @@
         <v>75</v>
       </c>
       <c r="AK73" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AL73" t="n">
         <v>55</v>
@@ -18993,16 +18993,16 @@
         <v>100</v>
       </c>
       <c r="AN73" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AO73" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AP73" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ73" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR73" t="n">
         <v>11.5</v>
@@ -19017,7 +19017,7 @@
         <v>6.4</v>
       </c>
       <c r="AV73" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AW73" t="n">
         <v>18</v>
@@ -19032,7 +19032,7 @@
         <v>13</v>
       </c>
       <c r="BA73" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BB73" t="n">
         <v>1.01</v>
@@ -19041,7 +19041,7 @@
         <v>1.01</v>
       </c>
       <c r="BD73" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BE73" t="n">
         <v>1.01</v>
@@ -19071,7 +19071,7 @@
         <v>5.4</v>
       </c>
       <c r="BN73" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BO73" t="n">
         <v>5.3</v>
@@ -19089,13 +19089,13 @@
         <v>5</v>
       </c>
       <c r="BT73" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU73" t="n">
         <v>4.1</v>
       </c>
       <c r="BV73" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BW73" t="n">
         <v>4.3</v>
@@ -19104,7 +19104,7 @@
         <v>34</v>
       </c>
       <c r="BY73" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BZ73" t="n">
         <v>28</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="CB74" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -19402,13 +19402,13 @@
         <v>2.32</v>
       </c>
       <c r="G75" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="H75" t="n">
         <v>3.3</v>
       </c>
       <c r="I75" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J75" t="n">
         <v>3.05</v>
@@ -19423,7 +19423,7 @@
         <v>1.1</v>
       </c>
       <c r="N75" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="O75" t="n">
         <v>1.4</v>
@@ -19447,10 +19447,10 @@
         <v>1.9</v>
       </c>
       <c r="V75" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W75" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="X75" t="n">
         <v>12.5</v>
@@ -19459,7 +19459,7 @@
         <v>13</v>
       </c>
       <c r="Z75" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA75" t="n">
         <v>80</v>
@@ -19507,7 +19507,7 @@
         <v>70</v>
       </c>
       <c r="AP75" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ75" t="n">
         <v>9.6</v>
@@ -19516,7 +19516,7 @@
         <v>18</v>
       </c>
       <c r="AS75" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT75" t="n">
         <v>7.4</v>
@@ -19528,19 +19528,19 @@
         <v>11.5</v>
       </c>
       <c r="AW75" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AX75" t="n">
         <v>11</v>
       </c>
       <c r="AY75" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ75" t="n">
         <v>17</v>
       </c>
       <c r="BA75" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BB75" t="n">
         <v>4.6</v>
@@ -19549,7 +19549,7 @@
         <v>4.5</v>
       </c>
       <c r="BD75" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BE75" t="n">
         <v>5</v>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="CB75" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -19653,13 +19653,13 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="G76" t="n">
         <v>990</v>
       </c>
       <c r="H76" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="I76" t="n">
         <v>990</v>
@@ -19876,7 +19876,7 @@
       </c>
       <c r="CB76" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -19916,13 +19916,13 @@
         <v>4.1</v>
       </c>
       <c r="I77" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="J77" t="n">
         <v>3.4</v>
       </c>
       <c r="K77" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L77" t="n">
         <v>1.01</v>
@@ -19943,130 +19943,130 @@
         <v>2.12</v>
       </c>
       <c r="R77" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S77" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T77" t="n">
         <v>1.78</v>
       </c>
       <c r="U77" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V77" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W77" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="X77" t="n">
         <v>14</v>
       </c>
       <c r="Y77" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="Z77" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AA77" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB77" t="n">
         <v>8.4</v>
       </c>
       <c r="AC77" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD77" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AE77" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AF77" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AG77" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH77" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AI77" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AJ77" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AK77" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AL77" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AM77" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN77" t="n">
         <v>21</v>
       </c>
       <c r="AO77" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AP77" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="AQ77" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AR77" t="n">
-        <v>8.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="AS77" t="n">
-        <v>10</v>
+        <v>5.6</v>
       </c>
       <c r="AT77" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU77" t="n">
         <v>7</v>
       </c>
       <c r="AV77" t="n">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="AW77" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX77" t="n">
         <v>10.5</v>
       </c>
       <c r="AY77" t="n">
-        <v>9.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="AZ77" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA77" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="BB77" t="n">
-        <v>7.6</v>
+        <v>4.9</v>
       </c>
       <c r="BC77" t="n">
-        <v>7.6</v>
+        <v>4.9</v>
       </c>
       <c r="BD77" t="n">
-        <v>8.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="BE77" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="BF77" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BG77" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="BH77" t="n">
         <v>1000</v>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="CB77" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -20161,7 +20161,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="G78" t="n">
         <v>1.94</v>
@@ -20173,10 +20173,10 @@
         <v>5.3</v>
       </c>
       <c r="J78" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K78" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L78" t="n">
         <v>1.37</v>
@@ -20191,7 +20191,7 @@
         <v>1.37</v>
       </c>
       <c r="P78" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q78" t="n">
         <v>2.04</v>
@@ -20200,13 +20200,13 @@
         <v>1.3</v>
       </c>
       <c r="S78" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="T78" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="U78" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="V78" t="n">
         <v>1.23</v>
@@ -20215,13 +20215,13 @@
         <v>2.06</v>
       </c>
       <c r="X78" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="Y78" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="Z78" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AA78" t="n">
         <v>150</v>
@@ -20230,34 +20230,34 @@
         <v>9.6</v>
       </c>
       <c r="AC78" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AD78" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AE78" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AF78" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AG78" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH78" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AI78" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AJ78" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AK78" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AL78" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AM78" t="n">
         <v>160</v>
@@ -20269,58 +20269,58 @@
         <v>110</v>
       </c>
       <c r="AP78" t="n">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="AQ78" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="AR78" t="n">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="AS78" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="AT78" t="n">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="AU78" t="n">
         <v>7.2</v>
       </c>
       <c r="AV78" t="n">
-        <v>6.2</v>
+        <v>3.95</v>
       </c>
       <c r="AW78" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX78" t="n">
-        <v>5.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY78" t="n">
         <v>9</v>
       </c>
       <c r="AZ78" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="BA78" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="BB78" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="BC78" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="BD78" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BE78" t="n">
-        <v>8.6</v>
+        <v>4.6</v>
       </c>
       <c r="BF78" t="n">
         <v>11</v>
       </c>
       <c r="BG78" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH78" t="n">
         <v>3.7</v>
@@ -20335,7 +20335,7 @@
         <v>1.01</v>
       </c>
       <c r="BL78" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="BM78" t="n">
         <v>1.01</v>
@@ -20359,7 +20359,7 @@
         <v>1.01</v>
       </c>
       <c r="BT78" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BU78" t="n">
         <v>6</v>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="CB78" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
@@ -20418,7 +20418,7 @@
         <v>1.32</v>
       </c>
       <c r="G79" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="H79" t="n">
         <v>12.5</v>
@@ -20457,7 +20457,7 @@
         <v>3.3</v>
       </c>
       <c r="T79" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="U79" t="n">
         <v>1.64</v>
@@ -20466,7 +20466,7 @@
         <v>1.06</v>
       </c>
       <c r="W79" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="X79" t="n">
         <v>17.5</v>
@@ -20481,22 +20481,22 @@
         <v>1000</v>
       </c>
       <c r="AB79" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC79" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD79" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AE79" t="n">
         <v>330</v>
       </c>
       <c r="AF79" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG79" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH79" t="n">
         <v>42</v>
@@ -20508,7 +20508,7 @@
         <v>12</v>
       </c>
       <c r="AK79" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL79" t="n">
         <v>55</v>
@@ -20517,7 +20517,7 @@
         <v>300</v>
       </c>
       <c r="AN79" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AO79" t="n">
         <v>590</v>
@@ -20526,55 +20526,55 @@
         <v>14.5</v>
       </c>
       <c r="AQ79" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="AR79" t="n">
-        <v>8.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="AS79" t="n">
-        <v>9.4</v>
+        <v>5.9</v>
       </c>
       <c r="AT79" t="n">
         <v>6.2</v>
       </c>
       <c r="AU79" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="AV79" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="AW79" t="n">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="AX79" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY79" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ79" t="n">
-        <v>7.6</v>
+        <v>28</v>
       </c>
       <c r="BA79" t="n">
-        <v>9.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="BB79" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD79" t="n">
         <v>5.3</v>
       </c>
-      <c r="BC79" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD79" t="n">
-        <v>8</v>
-      </c>
       <c r="BE79" t="n">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="BF79" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BG79" t="n">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="BH79" t="n">
         <v>1000</v>
@@ -20638,7 +20638,7 @@
       </c>
       <c r="CB79" t="inlineStr">
         <is>
-          <t>2026-05-14 05:13:55</t>
+          <t>2026-05-14 07:35:27</t>
         </is>
       </c>
     </row>
